--- a/technicals/exports/2026-10-02.xlsx
+++ b/technicals/exports/2026-10-02.xlsx
@@ -153,7 +153,7 @@
         <ns0:v>-0.7965613232345459</ns0:v>
       </ns0:c>
       <ns0:c r="K2">
-        <ns0:v>0.8605910629107434</ns0:v>
+        <ns0:v>0.8829402214442845</ns0:v>
       </ns0:c>
       <ns0:c r="L2">
         <ns0:v>70.0723975533013</ns0:v>
@@ -232,7 +232,7 @@
         <ns0:v>3.3218640186959414</ns0:v>
       </ns0:c>
       <ns0:c r="K3">
-        <ns0:v>1.1247187851300389</ns0:v>
+        <ns0:v>1.1268649710891174</ns0:v>
       </ns0:c>
       <ns0:c r="L3">
         <ns0:v>69.51043934537475</ns0:v>
@@ -356,55 +356,55 @@
       </ns0:c>
       <ns0:c r="B5" t="inlineStr">
         <ns0:is>
-          <ns0:t>ALNT</ns0:t>
+          <ns0:t>ACA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C5" t="inlineStr">
         <ns0:is>
-          <ns0:t>Allient Inc</ns0:t>
+          <ns0:t>Arcosa Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D5" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Industrials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E5" t="inlineStr">
         <ns0:is>
-          <ns0:t>Electronic Components</ns0:t>
+          <ns0:t>Engineering &amp; Construction</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F5" t="inlineStr">
         <ns0:is>
-          <ns0:t>다양한 산업용 정밀·특수 모션 제어 부품과 시스템을 설계·제조·판매하는 기업.</ns0:t>
+          <ns0:t>미국 건설·엔지니어링 구조물·운송 시장에 인프라 관련 제품과 솔루션을 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G5">
-        <ns0:v>118.30000305175781</ns0:v>
+        <ns0:v>146.5</ns0:v>
       </ns0:c>
       <ns0:c r="H5">
-        <ns0:v>2.026740979186581</ns0:v>
+        <ns0:v>0.0</ns0:v>
       </ns0:c>
       <ns0:c r="I5">
-        <ns0:v>118.66999816894531</ns0:v>
+        <ns0:v>146.9199981689453</ns0:v>
       </ns0:c>
       <ns0:c r="J5">
-        <ns0:v>-0.311784884887889</ns0:v>
+        <ns0:v>-0.2858686184179948</ns0:v>
       </ns0:c>
       <ns0:c r="K5">
-        <ns0:v>0.9068453976764969</ns0:v>
+        <ns0:v>0.4731666123637718</ns0:v>
       </ns0:c>
       <ns0:c r="L5">
-        <ns0:v>67.28054254779053</ns0:v>
+        <ns0:v>63.28940085866867</ns0:v>
       </ns0:c>
       <ns0:c r="M5">
-        <ns0:v>104.35650024414062</ns0:v>
+        <ns0:v>145.88049850463867</ns0:v>
       </ns0:c>
       <ns0:c r="N5">
-        <ns0:v>100.13799987792969</ns0:v>
+        <ns0:v>145.46619903564454</ns0:v>
       </ns0:c>
       <ns0:c r="O5">
-        <ns0:v>78.2552999305725</ns0:v>
+        <ns0:v>127.18264972686768</ns0:v>
       </ns0:c>
       <ns0:c r="P5" t="inlineStr">
         <ns0:is>
@@ -423,7 +423,7 @@
       </ns0:c>
       <ns0:c r="T5" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/ALNT/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/ACA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -435,12 +435,12 @@
       </ns0:c>
       <ns0:c r="B6" t="inlineStr">
         <ns0:is>
-          <ns0:t>ASX</ns0:t>
+          <ns0:t>ALNT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C6" t="inlineStr">
         <ns0:is>
-          <ns0:t>ASE Technology Holding CoLtd ADR</ns0:t>
+          <ns0:t>Allient Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D6" t="inlineStr">
@@ -450,44 +450,44 @@
       </ns0:c>
       <ns0:c r="E6" t="inlineStr">
         <ns0:is>
-          <ns0:t>Semiconductors</ns0:t>
+          <ns0:t>Electronic Components</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F6" t="inlineStr">
         <ns0:is>
-          <ns0:t>반도체 패키징·테스트와 전자제품 제조 서비스를 전 세계에 제공하는 기업.</ns0:t>
+          <ns0:t>다양한 산업용 정밀·특수 모션 제어 부품과 시스템을 설계·제조·판매하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G6">
-        <ns0:v>47.45000076293945</ns0:v>
+        <ns0:v>118.30000305175781</ns0:v>
       </ns0:c>
       <ns0:c r="H6">
-        <ns0:v>6.080932815871742</ns0:v>
+        <ns0:v>2.026740979186581</ns0:v>
       </ns0:c>
       <ns0:c r="I6">
-        <ns0:v>45.75</ns0:v>
+        <ns0:v>118.66999816894531</ns0:v>
       </ns0:c>
       <ns0:c r="J6">
-        <ns0:v>3.7158486621627462</ns0:v>
+        <ns0:v>-0.311784884887889</ns0:v>
       </ns0:c>
       <ns0:c r="K6">
-        <ns0:v>1.1636888481113459</ns0:v>
+        <ns0:v>0.9070598748882931</ns0:v>
       </ns0:c>
       <ns0:c r="L6">
-        <ns0:v>69.0039597391648</ns0:v>
+        <ns0:v>67.28054254779053</ns0:v>
       </ns0:c>
       <ns0:c r="M6">
-        <ns0:v>41.90050048828125</ns0:v>
+        <ns0:v>104.35650024414062</ns0:v>
       </ns0:c>
       <ns0:c r="N6">
-        <ns0:v>38.98080020904541</ns0:v>
+        <ns0:v>100.13799987792969</ns0:v>
       </ns0:c>
       <ns0:c r="O6">
-        <ns0:v>30.671150002479553</ns0:v>
+        <ns0:v>78.2552999305725</ns0:v>
       </ns0:c>
       <ns0:c r="P6" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q6" t="inlineStr">
@@ -502,7 +502,7 @@
       </ns0:c>
       <ns0:c r="T6" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/ASX/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/ALNT/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -514,59 +514,59 @@
       </ns0:c>
       <ns0:c r="B7" t="inlineStr">
         <ns0:is>
-          <ns0:t>ATKR</ns0:t>
+          <ns0:t>ARW</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C7" t="inlineStr">
         <ns0:is>
-          <ns0:t>Atkore Inc</ns0:t>
+          <ns0:t>Arrow Electronics Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D7" t="inlineStr">
         <ns0:is>
-          <ns0:t>Industrials</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E7" t="inlineStr">
         <ns0:is>
-          <ns0:t>Electrical Equipment &amp; Parts</ns0:t>
+          <ns0:t>Electronics &amp; Computer Distribution</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F7" t="inlineStr">
         <ns0:is>
-          <ns0:t>전기·기계·안전·인프라 제품과 솔루션을 제조·판매하는 기업.</ns0:t>
+          <ns0:t>전 세계 제조업체·서비스 제공업체·기업용 컴퓨팅 사용자를 위해 기술 조달과 설계를 수행한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G7">
-        <ns0:v>94.62000274658203</ns0:v>
+        <ns0:v>242.00999450683594</ns0:v>
       </ns0:c>
       <ns0:c r="H7">
-        <ns0:v>-0.1582715013162872</ns0:v>
+        <ns0:v>4.481280233653218</ns0:v>
       </ns0:c>
       <ns0:c r="I7">
-        <ns0:v>94.83999633789062</ns0:v>
+        <ns0:v>237.3300018310547</ns0:v>
       </ns0:c>
       <ns0:c r="J7">
-        <ns0:v>-0.23196288465133774</ns0:v>
+        <ns0:v>1.971934706810785</ns0:v>
       </ns0:c>
       <ns0:c r="K7">
-        <ns0:v>1.6483863338553486</ns0:v>
+        <ns0:v>2.099039309416624</ns0:v>
       </ns0:c>
       <ns0:c r="L7">
-        <ns0:v>69.65214636769144</ns0:v>
+        <ns0:v>69.00662230657379</ns0:v>
       </ns0:c>
       <ns0:c r="M7">
-        <ns0:v>94.40700073242188</ns0:v>
+        <ns0:v>222.58350143432617</ns0:v>
       </ns0:c>
       <ns0:c r="N7">
-        <ns0:v>91.60560043334961</ns0:v>
+        <ns0:v>215.46580078125</ns0:v>
       </ns0:c>
       <ns0:c r="O7">
-        <ns0:v>75.38070016860962</ns0:v>
+        <ns0:v>180.19135063171387</ns0:v>
       </ns0:c>
       <ns0:c r="P7" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q7" t="inlineStr">
@@ -581,7 +581,7 @@
       </ns0:c>
       <ns0:c r="T7" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/ATKR/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/ARW/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -593,12 +593,12 @@
       </ns0:c>
       <ns0:c r="B8" t="inlineStr">
         <ns0:is>
-          <ns0:t>AUDC</ns0:t>
+          <ns0:t>ASX</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C8" t="inlineStr">
         <ns0:is>
-          <ns0:t>Audiocodes</ns0:t>
+          <ns0:t>ASE Technology Holding CoLtd ADR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D8" t="inlineStr">
@@ -608,40 +608,40 @@
       </ns0:c>
       <ns0:c r="E8" t="inlineStr">
         <ns0:is>
-          <ns0:t>Communication Equipment</ns0:t>
+          <ns0:t>Semiconductors</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F8" t="inlineStr">
         <ns0:is>
-          <ns0:t>기업·컨택센터·통신사업자에 음성 통신 인프라·장비, 클라우드 관리 및 음성 AI 솔루션 제공.</ns0:t>
+          <ns0:t>반도체 패키징·테스트와 전자제품 제조 서비스를 전 세계에 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G8">
-        <ns0:v>11.09000015258789</ns0:v>
+        <ns0:v>47.45000076293945</ns0:v>
       </ns0:c>
       <ns0:c r="H8">
-        <ns0:v>1.4638594962924412</ns0:v>
+        <ns0:v>6.080932815871742</ns0:v>
       </ns0:c>
       <ns0:c r="I8">
-        <ns0:v>11.029999732971191</ns0:v>
+        <ns0:v>45.75</ns0:v>
       </ns0:c>
       <ns0:c r="J8">
-        <ns0:v>0.543974805705072</ns0:v>
+        <ns0:v>3.7158486621627462</ns0:v>
       </ns0:c>
       <ns0:c r="K8">
-        <ns0:v>1.4183601962158374</ns0:v>
+        <ns0:v>1.1647855139701555</ns0:v>
       </ns0:c>
       <ns0:c r="L8">
-        <ns0:v>69.95965713701686</ns0:v>
+        <ns0:v>69.0039597391648</ns0:v>
       </ns0:c>
       <ns0:c r="M8">
-        <ns0:v>10.218999910354615</ns0:v>
+        <ns0:v>41.90050048828125</ns0:v>
       </ns0:c>
       <ns0:c r="N8">
-        <ns0:v>10.011799983978271</ns0:v>
+        <ns0:v>38.98080020904541</ns0:v>
       </ns0:c>
       <ns0:c r="O8">
-        <ns0:v>9.079650011062622</ns0:v>
+        <ns0:v>30.671150002479553</ns0:v>
       </ns0:c>
       <ns0:c r="P8" t="inlineStr">
         <ns0:is>
@@ -660,7 +660,7 @@
       </ns0:c>
       <ns0:c r="T8" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/AUDC/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/ASX/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -672,59 +672,59 @@
       </ns0:c>
       <ns0:c r="B9" t="inlineStr">
         <ns0:is>
-          <ns0:t>AVT</ns0:t>
+          <ns0:t>ATKR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C9" t="inlineStr">
         <ns0:is>
-          <ns0:t>Avnet Inc</ns0:t>
+          <ns0:t>Atkore Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D9" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Industrials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E9" t="inlineStr">
         <ns0:is>
-          <ns0:t>Electronics &amp; Computer Distribution</ns0:t>
+          <ns0:t>Electrical Equipment &amp; Parts</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F9" t="inlineStr">
         <ns0:is>
-          <ns0:t>반도체, 연결 부품, 수동 및 전기기계 부품 등 전자부품을 전 세계에 유통하는 기업.</ns0:t>
+          <ns0:t>전기·기계·안전·인프라 제품과 솔루션을 제조·판매하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G9">
-        <ns0:v>106.93499755859375</ns0:v>
+        <ns0:v>94.62000274658203</ns0:v>
       </ns0:c>
       <ns0:c r="H9">
-        <ns0:v>4.592135947694476</ns0:v>
+        <ns0:v>-0.1582715013162872</ns0:v>
       </ns0:c>
       <ns0:c r="I9">
-        <ns0:v>104.58000183105469</ns0:v>
+        <ns0:v>94.83999633789062</ns0:v>
       </ns0:c>
       <ns0:c r="J9">
-        <ns0:v>2.251860476483336</ns0:v>
+        <ns0:v>-0.23196288465133774</ns0:v>
       </ns0:c>
       <ns0:c r="K9">
-        <ns0:v>1.5790337937803038</ns0:v>
+        <ns0:v>1.721499568538464</ns0:v>
       </ns0:c>
       <ns0:c r="L9">
-        <ns0:v>68.09215622045187</ns0:v>
+        <ns0:v>69.65214636769144</ns0:v>
       </ns0:c>
       <ns0:c r="M9">
-        <ns0:v>97.38574981689453</ns0:v>
+        <ns0:v>94.40700073242188</ns0:v>
       </ns0:c>
       <ns0:c r="N9">
-        <ns0:v>93.70449935913086</ns0:v>
+        <ns0:v>91.60560043334961</ns0:v>
       </ns0:c>
       <ns0:c r="O9">
-        <ns0:v>76.47762474060059</ns0:v>
+        <ns0:v>75.38070016860962</ns0:v>
       </ns0:c>
       <ns0:c r="P9" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q9" t="inlineStr">
@@ -739,7 +739,7 @@
       </ns0:c>
       <ns0:c r="T9" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/AVT/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/ATKR/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -751,59 +751,59 @@
       </ns0:c>
       <ns0:c r="B10" t="inlineStr">
         <ns0:is>
-          <ns0:t>AZTA</ns0:t>
+          <ns0:t>AUDC</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C10" t="inlineStr">
         <ns0:is>
-          <ns0:t>Azenta Inc</ns0:t>
+          <ns0:t>Audiocodes</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D10" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E10" t="inlineStr">
         <ns0:is>
-          <ns0:t>Medical Instruments &amp; Supplies</ns0:t>
+          <ns0:t>Communication Equipment</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F10" t="inlineStr">
         <ns0:is>
-          <ns0:t>생명과학 산업에 생물학적·화학적 화합물 시료 탐색 및 관리 솔루션을 제공하는 기업.</ns0:t>
+          <ns0:t>기업·컨택센터·통신사업자에 음성 통신 인프라·장비, 클라우드 관리 및 음성 AI 솔루션 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G10">
-        <ns0:v>38.75</ns0:v>
+        <ns0:v>11.09000015258789</ns0:v>
       </ns0:c>
       <ns0:c r="H10">
-        <ns0:v>12.383992211290874</ns0:v>
+        <ns0:v>1.4638594962924412</ns0:v>
       </ns0:c>
       <ns0:c r="I10">
-        <ns0:v>41.72999954223633</ns0:v>
+        <ns0:v>11.029999732971191</ns0:v>
       </ns0:c>
       <ns0:c r="J10">
-        <ns0:v>-7.141144440272928</ns0:v>
+        <ns0:v>0.543974805705072</ns0:v>
       </ns0:c>
       <ns0:c r="K10">
-        <ns0:v>3.9034810660001744</ns0:v>
+        <ns0:v>1.4183601962158374</ns0:v>
       </ns0:c>
       <ns0:c r="L10">
-        <ns0:v>76.60255533341098</ns0:v>
+        <ns0:v>69.95965713701686</ns0:v>
       </ns0:c>
       <ns0:c r="M10">
-        <ns0:v>33.273499965667725</ns0:v>
+        <ns0:v>10.218999910354615</ns0:v>
       </ns0:c>
       <ns0:c r="N10">
-        <ns0:v>32.52180004119873</ns0:v>
+        <ns0:v>10.011799983978271</ns0:v>
       </ns0:c>
       <ns0:c r="O10">
-        <ns0:v>28.172299947738647</ns0:v>
+        <ns0:v>9.079650011062622</ns0:v>
       </ns0:c>
       <ns0:c r="P10" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q10" t="inlineStr">
@@ -818,7 +818,7 @@
       </ns0:c>
       <ns0:c r="T10" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/AZTA/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/AUDC/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -830,59 +830,59 @@
       </ns0:c>
       <ns0:c r="B11" t="inlineStr">
         <ns0:is>
-          <ns0:t>BPRN</ns0:t>
+          <ns0:t>AVT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C11" t="inlineStr">
         <ns0:is>
-          <ns0:t>Princeton Bancorp Inc</ns0:t>
+          <ns0:t>Avnet Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D11" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E11" t="inlineStr">
         <ns0:is>
-          <ns0:t>Banks - Regional</ns0:t>
+          <ns0:t>Electronics &amp; Computer Distribution</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F11" t="inlineStr">
         <ns0:is>
-          <ns0:t>다양한 예금 등 은행 상품·서비스를 제공하는 프린스턴은행의 은행지주회사.</ns0:t>
+          <ns0:t>반도체, 연결 부품, 수동 및 전기기계 부품 등 전자부품을 전 세계에 유통하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G11">
-        <ns0:v>43.720001220703125</ns0:v>
+        <ns0:v>106.94000244140625</ns0:v>
       </ns0:c>
       <ns0:c r="H11">
-        <ns0:v>1.297500869487589</ns0:v>
+        <ns0:v>4.597031177464683</ns0:v>
       </ns0:c>
       <ns0:c r="I11">
-        <ns0:v>44.099998474121094</ns0:v>
+        <ns0:v>104.58000183105469</ns0:v>
       </ns0:c>
       <ns0:c r="J11">
-        <ns0:v>-0.8616718062721906</ns0:v>
+        <ns0:v>2.256646174250476</ns0:v>
       </ns0:c>
       <ns0:c r="K11">
-        <ns0:v>1.0239418416801291</ns0:v>
+        <ns0:v>1.5790206102509265</ns0:v>
       </ns0:c>
       <ns0:c r="L11">
-        <ns0:v>57.044732776583274</ns0:v>
+        <ns0:v>68.09762544977696</ns0:v>
       </ns0:c>
       <ns0:c r="M11">
-        <ns0:v>43.34949970245361</ns0:v>
+        <ns0:v>97.38600006103516</ns0:v>
       </ns0:c>
       <ns0:c r="N11">
-        <ns0:v>42.711399993896485</ns0:v>
+        <ns0:v>93.70459945678711</ns0:v>
       </ns0:c>
       <ns0:c r="O11">
-        <ns0:v>37.46737504959106</ns0:v>
+        <ns0:v>76.47764976501465</ns0:v>
       </ns0:c>
       <ns0:c r="P11" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q11" t="inlineStr">
@@ -897,7 +897,7 @@
       </ns0:c>
       <ns0:c r="T11" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/BPRN/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/AVT/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -909,59 +909,59 @@
       </ns0:c>
       <ns0:c r="B12" t="inlineStr">
         <ns0:is>
-          <ns0:t>CBNK</ns0:t>
+          <ns0:t>AZTA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C12" t="inlineStr">
         <ns0:is>
-          <ns0:t>Capital Bancorp Inc</ns0:t>
+          <ns0:t>Azenta Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D12" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E12" t="inlineStr">
         <ns0:is>
-          <ns0:t>Banks - Regional</ns0:t>
+          <ns0:t>Medical Instruments &amp; Supplies</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F12" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 기업·비영리단체·기업가에 은행 상품과 서비스를 제공하는 캐피털은행의 지주회사.</ns0:t>
+          <ns0:t>생명과학 산업에 생물학적·화학적 화합물 시료 탐색 및 관리 솔루션을 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G12">
-        <ns0:v>40.45000076293945</ns0:v>
+        <ns0:v>38.75</ns0:v>
       </ns0:c>
       <ns0:c r="H12">
-        <ns0:v>1.6331696943191032</ns0:v>
+        <ns0:v>12.383992211290874</ns0:v>
       </ns0:c>
       <ns0:c r="I12">
-        <ns0:v>40.2599983215332</ns0:v>
+        <ns0:v>41.72999954223633</ns0:v>
       </ns0:c>
       <ns0:c r="J12">
-        <ns0:v>0.47193852291997906</ns0:v>
+        <ns0:v>-7.141144440272928</ns0:v>
       </ns0:c>
       <ns0:c r="K12">
-        <ns0:v>4.646595941909569</ns0:v>
+        <ns0:v>3.903629864279694</ns0:v>
       </ns0:c>
       <ns0:c r="L12">
-        <ns0:v>76.83447574965246</ns0:v>
+        <ns0:v>76.60255533341098</ns0:v>
       </ns0:c>
       <ns0:c r="M12">
-        <ns0:v>36.70650024414063</ns0:v>
+        <ns0:v>33.273499965667725</ns0:v>
       </ns0:c>
       <ns0:c r="N12">
-        <ns0:v>36.908200149536135</ns0:v>
+        <ns0:v>32.52180004119873</ns0:v>
       </ns0:c>
       <ns0:c r="O12">
-        <ns0:v>32.71664995193481</ns0:v>
+        <ns0:v>28.172299947738647</ns0:v>
       </ns0:c>
       <ns0:c r="P12" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q12" t="inlineStr">
@@ -976,7 +976,7 @@
       </ns0:c>
       <ns0:c r="T12" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/CBNK/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/AZTA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -988,55 +988,55 @@
       </ns0:c>
       <ns0:c r="B13" t="inlineStr">
         <ns0:is>
-          <ns0:t>CDNA</ns0:t>
+          <ns0:t>BPRN</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C13" t="inlineStr">
         <ns0:is>
-          <ns0:t>Caredx Inc</ns0:t>
+          <ns0:t>Princeton Bancorp Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D13" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E13" t="inlineStr">
         <ns0:is>
-          <ns0:t>Diagnostics &amp; Research</ns0:t>
+          <ns0:t>Banks - Regional</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F13" t="inlineStr">
         <ns0:is>
-          <ns0:t>이식 환자의 치료 결과와 장기 건강 개선을 위한 솔루션을 제공하는 기업.</ns0:t>
+          <ns0:t>다양한 예금 등 은행 상품·서비스를 제공하는 프린스턴은행의 은행지주회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G13">
-        <ns0:v>67.1500015258789</ns0:v>
+        <ns0:v>43.720001220703125</ns0:v>
       </ns0:c>
       <ns0:c r="H13">
-        <ns0:v>1.389095760704051</ns0:v>
+        <ns0:v>1.297500869487589</ns0:v>
       </ns0:c>
       <ns0:c r="I13">
-        <ns0:v>67.29000091552734</ns0:v>
+        <ns0:v>44.099998474121094</ns0:v>
       </ns0:c>
       <ns0:c r="J13">
-        <ns0:v>-0.20805377878384546</ns0:v>
+        <ns0:v>-0.8616718062721906</ns0:v>
       </ns0:c>
       <ns0:c r="K13">
-        <ns0:v>1.2136831173591331</ns0:v>
+        <ns0:v>1.024232633279483</ns0:v>
       </ns0:c>
       <ns0:c r="L13">
-        <ns0:v>81.29879642750278</ns0:v>
+        <ns0:v>57.044732776583274</ns0:v>
       </ns0:c>
       <ns0:c r="M13">
-        <ns0:v>56.76750011444092</ns0:v>
+        <ns0:v>43.34949970245361</ns0:v>
       </ns0:c>
       <ns0:c r="N13">
-        <ns0:v>50.253800048828126</ns0:v>
+        <ns0:v>42.711399993896485</ns0:v>
       </ns0:c>
       <ns0:c r="O13">
-        <ns0:v>28.757974948883056</ns0:v>
+        <ns0:v>37.46737504959106</ns0:v>
       </ns0:c>
       <ns0:c r="P13" t="inlineStr">
         <ns0:is>
@@ -1055,7 +1055,7 @@
       </ns0:c>
       <ns0:c r="T13" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/CDNA/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/BPRN/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1067,59 +1067,59 @@
       </ns0:c>
       <ns0:c r="B14" t="inlineStr">
         <ns0:is>
-          <ns0:t>CHEF</ns0:t>
+          <ns0:t>CBNK</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C14" t="inlineStr">
         <ns0:is>
-          <ns0:t>Chefs' Warehouse Inc</ns0:t>
+          <ns0:t>Capital Bancorp Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D14" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Defensive</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E14" t="inlineStr">
         <ns0:is>
-          <ns0:t>Food Distribution</ns0:t>
+          <ns0:t>Banks - Regional</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F14" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·중동·캐나다에서 특수 식재료와 주 요리용 식품을 유통하는 기업.</ns0:t>
+          <ns0:t>미국 기업·비영리단체·기업가에 은행 상품과 서비스를 제공하는 캐피털은행의 지주회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G14">
-        <ns0:v>116.41999816894531</ns0:v>
+        <ns0:v>40.45000076293945</ns0:v>
       </ns0:c>
       <ns0:c r="H14">
-        <ns0:v>3.4292827772514967</ns0:v>
+        <ns0:v>1.6331696943191032</ns0:v>
       </ns0:c>
       <ns0:c r="I14">
-        <ns0:v>117.6500015258789</ns0:v>
+        <ns0:v>40.2599983215332</ns0:v>
       </ns0:c>
       <ns0:c r="J14">
-        <ns0:v>-1.0454767029161816</ns0:v>
+        <ns0:v>0.47193852291997906</ns0:v>
       </ns0:c>
       <ns0:c r="K14">
-        <ns0:v>0.9999209304899938</ns0:v>
+        <ns0:v>4.684313523534865</ns0:v>
       </ns0:c>
       <ns0:c r="L14">
-        <ns0:v>63.76376771593809</ns0:v>
+        <ns0:v>76.83447574965246</ns0:v>
       </ns0:c>
       <ns0:c r="M14">
-        <ns0:v>110.78549919128417</ns0:v>
+        <ns0:v>36.70650024414063</ns0:v>
       </ns0:c>
       <ns0:c r="N14">
-        <ns0:v>110.07979949951172</ns0:v>
+        <ns0:v>36.908200149536135</ns0:v>
       </ns0:c>
       <ns0:c r="O14">
-        <ns0:v>82.26124982833862</ns0:v>
+        <ns0:v>32.71664995193481</ns0:v>
       </ns0:c>
       <ns0:c r="P14" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q14" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </ns0:c>
       <ns0:c r="T14" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/CHEF/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/CBNK/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1146,55 +1146,55 @@
       </ns0:c>
       <ns0:c r="B15" t="inlineStr">
         <ns0:is>
-          <ns0:t>CNXN</ns0:t>
+          <ns0:t>CDNA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C15" t="inlineStr">
         <ns0:is>
-          <ns0:t>PC Connection Inc</ns0:t>
+          <ns0:t>Caredx Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D15" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E15" t="inlineStr">
         <ns0:is>
-          <ns0:t>Electronics &amp; Computer Distribution</ns0:t>
+          <ns0:t>Diagnostics &amp; Research</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F15" t="inlineStr">
         <ns0:is>
-          <ns0:t>기업·공공부문 등에 컴퓨터 시스템과 데이터센터를 포함한 다양한 IT 솔루션을 제공하는 기업.</ns0:t>
+          <ns0:t>이식 환자의 치료 결과와 장기 건강 개선을 위한 솔루션을 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G15">
-        <ns0:v>92.37999725341797</ns0:v>
+        <ns0:v>67.1500015258789</ns0:v>
       </ns0:c>
       <ns0:c r="H15">
-        <ns0:v>-0.20525271905869058</ns0:v>
+        <ns0:v>1.389095760704051</ns0:v>
       </ns0:c>
       <ns0:c r="I15">
-        <ns0:v>93.45999908447266</ns0:v>
+        <ns0:v>67.29000091552734</ns0:v>
       </ns0:c>
       <ns0:c r="J15">
-        <ns0:v>-1.1555765478646562</ns0:v>
+        <ns0:v>-0.20805377878384546</ns0:v>
       </ns0:c>
       <ns0:c r="K15">
-        <ns0:v>0.8520015092786334</ns0:v>
+        <ns0:v>1.212688134273082</ns0:v>
       </ns0:c>
       <ns0:c r="L15">
-        <ns0:v>76.02125170863214</ns0:v>
+        <ns0:v>81.29879642750278</ns0:v>
       </ns0:c>
       <ns0:c r="M15">
-        <ns0:v>87.21499938964844</ns0:v>
+        <ns0:v>56.76750011444092</ns0:v>
       </ns0:c>
       <ns0:c r="N15">
-        <ns0:v>83.70319976806641</ns0:v>
+        <ns0:v>50.253800048828126</ns0:v>
       </ns0:c>
       <ns0:c r="O15">
-        <ns0:v>69.28499990463257</ns0:v>
+        <ns0:v>28.757974948883056</ns0:v>
       </ns0:c>
       <ns0:c r="P15" t="inlineStr">
         <ns0:is>
@@ -1213,7 +1213,7 @@
       </ns0:c>
       <ns0:c r="T15" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/CNXN/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/CDNA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1225,55 +1225,55 @@
       </ns0:c>
       <ns0:c r="B16" t="inlineStr">
         <ns0:is>
-          <ns0:t>COHU</ns0:t>
+          <ns0:t>CHEF</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C16" t="inlineStr">
         <ns0:is>
-          <ns0:t>Cohu Inc</ns0:t>
+          <ns0:t>Chefs' Warehouse Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D16" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Consumer Defensive</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E16" t="inlineStr">
         <ns0:is>
-          <ns0:t>Semiconductor Equipment &amp; Materials</ns0:t>
+          <ns0:t>Food Distribution</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F16" t="inlineStr">
         <ns0:is>
-          <ns0:t>반도체 테스트 장비·서비스와 검사·계측 자동화 시스템 등을 제공하는 기업.</ns0:t>
+          <ns0:t>미국·중동·캐나다에서 특수 식재료와 주 요리용 식품을 유통하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G16">
-        <ns0:v>73.4800033569336</ns0:v>
+        <ns0:v>116.41999816894531</ns0:v>
       </ns0:c>
       <ns0:c r="H16">
-        <ns0:v>4.464042056470108</ns0:v>
+        <ns0:v>3.4292827772514967</ns0:v>
       </ns0:c>
       <ns0:c r="I16">
-        <ns0:v>74.5999984741211</ns0:v>
+        <ns0:v>117.6500015258789</ns0:v>
       </ns0:c>
       <ns0:c r="J16">
-        <ns0:v>-1.5013339679571525</ns0:v>
+        <ns0:v>-1.0454767029161816</ns0:v>
       </ns0:c>
       <ns0:c r="K16">
-        <ns0:v>1.3550007530498518</ns0:v>
+        <ns0:v>1.0000711625590055</ns0:v>
       </ns0:c>
       <ns0:c r="L16">
-        <ns0:v>73.23887687704554</ns0:v>
+        <ns0:v>63.76376771593809</ns0:v>
       </ns0:c>
       <ns0:c r="M16">
-        <ns0:v>60.02350044250488</ns0:v>
+        <ns0:v>110.78549919128417</ns0:v>
       </ns0:c>
       <ns0:c r="N16">
-        <ns0:v>54.590800247192384</ns0:v>
+        <ns0:v>110.07979949951172</ns0:v>
       </ns0:c>
       <ns0:c r="O16">
-        <ns0:v>43.81070007324219</ns0:v>
+        <ns0:v>82.26124982833862</ns0:v>
       </ns0:c>
       <ns0:c r="P16" t="inlineStr">
         <ns0:is>
@@ -1292,7 +1292,7 @@
       </ns0:c>
       <ns0:c r="T16" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/COHU/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/CHEF/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1304,12 +1304,12 @@
       </ns0:c>
       <ns0:c r="B17" t="inlineStr">
         <ns0:is>
-          <ns0:t>CRWD</ns0:t>
+          <ns0:t>CNXN</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C17" t="inlineStr">
         <ns0:is>
-          <ns0:t>Crowdstrike Holdings Inc</ns0:t>
+          <ns0:t>PC Connection Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D17" t="inlineStr">
@@ -1319,44 +1319,44 @@
       </ns0:c>
       <ns0:c r="E17" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Infrastructure</ns0:t>
+          <ns0:t>Electronics &amp; Computer Distribution</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F17" t="inlineStr">
         <ns0:is>
-          <ns0:t>구독형 통합 플랫폼으로 엔드포인트·클라우드 워크로드·신원·데이터를 보호하는 사이버보안 기업.</ns0:t>
+          <ns0:t>기업·공공부문 등에 컴퓨터 시스템과 데이터센터를 포함한 다양한 IT 솔루션을 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G17">
-        <ns0:v>270.0400085449219</ns0:v>
+        <ns0:v>92.37999725341797</ns0:v>
       </ns0:c>
       <ns0:c r="H17">
-        <ns0:v>1.4844647530512178</ns0:v>
+        <ns0:v>-0.20525271905869058</ns0:v>
       </ns0:c>
       <ns0:c r="I17">
-        <ns0:v>269.29998779296875</ns0:v>
+        <ns0:v>93.45999908447266</ns0:v>
       </ns0:c>
       <ns0:c r="J17">
-        <ns0:v>0.2747942018185512</ns0:v>
+        <ns0:v>-1.1555765478646562</ns0:v>
       </ns0:c>
       <ns0:c r="K17">
-        <ns0:v>0.5349421921959808</ns0:v>
+        <ns0:v>0.8520563921380304</ns0:v>
       </ns0:c>
       <ns0:c r="L17">
-        <ns0:v>68.74572609292409</ns0:v>
+        <ns0:v>76.02125170863214</ns0:v>
       </ns0:c>
       <ns0:c r="M17">
-        <ns0:v>242.28350143432618</ns0:v>
+        <ns0:v>87.21499938964844</ns0:v>
       </ns0:c>
       <ns0:c r="N17">
-        <ns0:v>219.79740020751953</ns0:v>
+        <ns0:v>83.70319976806641</ns0:v>
       </ns0:c>
       <ns0:c r="O17">
-        <ns0:v>153.54156242370607</ns0:v>
+        <ns0:v>69.28499990463257</ns0:v>
       </ns0:c>
       <ns0:c r="P17" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </ns0:c>
       <ns0:c r="T17" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/CRWD/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/CNXN/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1383,55 +1383,55 @@
       </ns0:c>
       <ns0:c r="B18" t="inlineStr">
         <ns0:is>
-          <ns0:t>CVI</ns0:t>
+          <ns0:t>COHU</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C18" t="inlineStr">
         <ns0:is>
-          <ns0:t>CVR Energy Inc</ns0:t>
+          <ns0:t>Cohu Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D18" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E18" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas Refining &amp; Marketing</ns0:t>
+          <ns0:t>Semiconductor Equipment &amp; Materials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F18" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 재생연료, 석유 정제·판매 및 질소비료 제조 사업을 영위하는 기업.</ns0:t>
+          <ns0:t>반도체 테스트 장비·서비스와 검사·계측 자동화 시스템 등을 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G18">
-        <ns0:v>54.83000183105469</ns0:v>
+        <ns0:v>73.4800033569336</ns0:v>
       </ns0:c>
       <ns0:c r="H18">
-        <ns0:v>0.86460856406545</ns0:v>
+        <ns0:v>4.464042056470108</ns0:v>
       </ns0:c>
       <ns0:c r="I18">
-        <ns0:v>55.189998626708984</ns0:v>
+        <ns0:v>74.5999984741211</ns0:v>
       </ns0:c>
       <ns0:c r="J18">
-        <ns0:v>-0.6522862921037986</ns0:v>
+        <ns0:v>-1.5013339679571525</ns0:v>
       </ns0:c>
       <ns0:c r="K18">
-        <ns0:v>0.6471921104667311</ns0:v>
+        <ns0:v>1.3557909533611125</ns0:v>
       </ns0:c>
       <ns0:c r="L18">
-        <ns0:v>74.6804658795747</ns0:v>
+        <ns0:v>73.23887687704554</ns0:v>
       </ns0:c>
       <ns0:c r="M18">
-        <ns0:v>50.98449993133545</ns0:v>
+        <ns0:v>60.02350044250488</ns0:v>
       </ns0:c>
       <ns0:c r="N18">
-        <ns0:v>42.307999801635745</ns0:v>
+        <ns0:v>54.590800247192384</ns0:v>
       </ns0:c>
       <ns0:c r="O18">
-        <ns0:v>32.3221999835968</ns0:v>
+        <ns0:v>43.81070007324219</ns0:v>
       </ns0:c>
       <ns0:c r="P18" t="inlineStr">
         <ns0:is>
@@ -1450,7 +1450,7 @@
       </ns0:c>
       <ns0:c r="T18" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/CVI/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/COHU/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1462,59 +1462,59 @@
       </ns0:c>
       <ns0:c r="B19" t="inlineStr">
         <ns0:is>
-          <ns0:t>CYRX</ns0:t>
+          <ns0:t>CRWD</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C19" t="inlineStr">
         <ns0:is>
-          <ns0:t>CryoPort Inc</ns0:t>
+          <ns0:t>Crowdstrike Holdings Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D19" t="inlineStr">
         <ns0:is>
-          <ns0:t>Industrials</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E19" t="inlineStr">
         <ns0:is>
-          <ns0:t>Integrated Freight &amp; Logistics</ns0:t>
+          <ns0:t>Software - Infrastructure</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F19" t="inlineStr">
         <ns0:is>
-          <ns0:t>바이오·제약, 동물 건강, 생식의학 분야에 온도 제어 물류·생물시료 보관 서비스를 제공.</ns0:t>
+          <ns0:t>구독형 통합 플랫폼으로 엔드포인트·클라우드 워크로드·신원·데이터를 보호하는 사이버보안 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G19">
-        <ns0:v>17.43000030517578</ns0:v>
+        <ns0:v>270.0400085449219</ns0:v>
       </ns0:c>
       <ns0:c r="H19">
-        <ns0:v>0.4032240343498472</ns0:v>
+        <ns0:v>1.4844647530512178</ns0:v>
       </ns0:c>
       <ns0:c r="I19">
-        <ns0:v>17.979999542236328</ns0:v>
+        <ns0:v>269.29998779296875</ns0:v>
       </ns0:c>
       <ns0:c r="J19">
-        <ns0:v>-3.0589502283832615</ns0:v>
+        <ns0:v>0.2747942018185512</ns0:v>
       </ns0:c>
       <ns0:c r="K19">
-        <ns0:v>1.10555720607321</ns0:v>
+        <ns0:v>0.5366094682672982</ns0:v>
       </ns0:c>
       <ns0:c r="L19">
-        <ns0:v>64.46316850464738</ns0:v>
+        <ns0:v>68.74572609292409</ns0:v>
       </ns0:c>
       <ns0:c r="M19">
-        <ns0:v>16.71000008583069</ns0:v>
+        <ns0:v>242.28350143432618</ns0:v>
       </ns0:c>
       <ns0:c r="N19">
-        <ns0:v>16.040399951934816</ns0:v>
+        <ns0:v>219.79740020751953</ns0:v>
       </ns0:c>
       <ns0:c r="O19">
-        <ns0:v>12.54055000782013</ns0:v>
+        <ns0:v>153.54156242370607</ns0:v>
       </ns0:c>
       <ns0:c r="P19" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q19" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </ns0:c>
       <ns0:c r="T19" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/CYRX/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/CRWD/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1541,59 +1541,59 @@
       </ns0:c>
       <ns0:c r="B20" t="inlineStr">
         <ns0:is>
-          <ns0:t>DAC</ns0:t>
+          <ns0:t>CVI</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C20" t="inlineStr">
         <ns0:is>
-          <ns0:t>Danaos Corp</ns0:t>
+          <ns0:t>CVR Energy Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D20" t="inlineStr">
         <ns0:is>
-          <ns0:t>Industrials</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E20" t="inlineStr">
         <ns0:is>
-          <ns0:t>Marine Shipping</ns0:t>
+          <ns0:t>Oil &amp; Gas Refining &amp; Marketing</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F20" t="inlineStr">
         <ns0:is>
-          <ns0:t>컨테이너선과 건화물선을 보유·운영하며 해상 운송 서비스를 제공하는 기업.</ns0:t>
+          <ns0:t>미국에서 재생연료, 석유 정제·판매 및 질소비료 제조 사업을 영위하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G20">
-        <ns0:v>165.14999389648438</ns0:v>
+        <ns0:v>54.83000183105469</ns0:v>
       </ns0:c>
       <ns0:c r="H20">
-        <ns0:v>2.1083147567126925</ns0:v>
+        <ns0:v>0.86460856406545</ns0:v>
       </ns0:c>
       <ns0:c r="I20">
-        <ns0:v>163.63999938964844</ns0:v>
+        <ns0:v>55.189998626708984</ns0:v>
       </ns0:c>
       <ns0:c r="J20">
-        <ns0:v>0.9227539186433598</ns0:v>
+        <ns0:v>-0.6522862921037986</ns0:v>
       </ns0:c>
       <ns0:c r="K20">
-        <ns0:v>1.6030936391760355</ns0:v>
+        <ns0:v>0.6507455509449449</ns0:v>
       </ns0:c>
       <ns0:c r="L20">
-        <ns0:v>69.74409295494817</ns0:v>
+        <ns0:v>74.6804658795747</ns0:v>
       </ns0:c>
       <ns0:c r="M20">
-        <ns0:v>157.38149948120116</ns0:v>
+        <ns0:v>50.98449993133545</ns0:v>
       </ns0:c>
       <ns0:c r="N20">
-        <ns0:v>149.80099975585938</ns0:v>
+        <ns0:v>42.307999801635745</ns0:v>
       </ns0:c>
       <ns0:c r="O20">
-        <ns0:v>124.1611499786377</ns0:v>
+        <ns0:v>32.3221999835968</ns0:v>
       </ns0:c>
       <ns0:c r="P20" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q20" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </ns0:c>
       <ns0:c r="T20" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/DAC/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/CVI/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1620,59 +1620,59 @@
       </ns0:c>
       <ns0:c r="B21" t="inlineStr">
         <ns0:is>
-          <ns0:t>DHT</ns0:t>
+          <ns0:t>CYRX</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C21" t="inlineStr">
         <ns0:is>
-          <ns0:t>DHT Holdings Inc</ns0:t>
+          <ns0:t>CryoPort Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D21" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Industrials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E21" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas Midstream</ns0:t>
+          <ns0:t>Integrated Freight &amp; Logistics</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F21" t="inlineStr">
         <ns0:is>
-          <ns0:t>자회사를 통해 원유 운반선을 소유·운영하며 기술 관리 서비스도 제공하는 기업.</ns0:t>
+          <ns0:t>바이오·제약, 동물 건강, 생식의학 분야에 온도 제어 물류·생물시료 보관 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G21">
-        <ns0:v>23.68000030517578</ns0:v>
+        <ns0:v>17.43000030517578</ns0:v>
       </ns0:c>
       <ns0:c r="H21">
-        <ns0:v>0.5093414344379266</ns0:v>
+        <ns0:v>0.4032240343498472</ns0:v>
       </ns0:c>
       <ns0:c r="I21">
-        <ns0:v>23.610000610351562</ns0:v>
+        <ns0:v>17.979999542236328</ns0:v>
       </ns0:c>
       <ns0:c r="J21">
-        <ns0:v>0.29648324021442907</ns0:v>
+        <ns0:v>-3.0589502283832615</ns0:v>
       </ns0:c>
       <ns0:c r="K21">
-        <ns0:v>0.7666437110457364</ns0:v>
+        <ns0:v>1.1100339311682017</ns0:v>
       </ns0:c>
       <ns0:c r="L21">
-        <ns0:v>70.40390194239433</ns0:v>
+        <ns0:v>64.46316850464738</ns0:v>
       </ns0:c>
       <ns0:c r="M21">
-        <ns0:v>22.122500133514404</ns0:v>
+        <ns0:v>16.71000008583069</ns0:v>
       </ns0:c>
       <ns0:c r="N21">
-        <ns0:v>20.253200073242187</ns0:v>
+        <ns0:v>16.040399951934816</ns0:v>
       </ns0:c>
       <ns0:c r="O21">
-        <ns0:v>17.545400009155273</ns0:v>
+        <ns0:v>12.54055000782013</ns0:v>
       </ns0:c>
       <ns0:c r="P21" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q21" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </ns0:c>
       <ns0:c r="T21" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/DHT/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/CYRX/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1699,59 +1699,59 @@
       </ns0:c>
       <ns0:c r="B22" t="inlineStr">
         <ns0:is>
-          <ns0:t>DT</ns0:t>
+          <ns0:t>DAC</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C22" t="inlineStr">
         <ns0:is>
-          <ns0:t>Dynatrace Inc</ns0:t>
+          <ns0:t>Danaos Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D22" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Industrials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E22" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Application</ns0:t>
+          <ns0:t>Marine Shipping</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F22" t="inlineStr">
         <ns0:is>
-          <ns0:t>디지털 기업의 복잡한 디지털 환경을 위한 AI 기반 관측성 플랫폼을 제공하는 기업.</ns0:t>
+          <ns0:t>컨테이너선과 건화물선을 보유·운영하며 해상 운송 서비스를 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G22">
-        <ns0:v>59.31999969482422</ns0:v>
+        <ns0:v>165.14999389648438</ns0:v>
       </ns0:c>
       <ns0:c r="H22">
-        <ns0:v>0.1012510546582579</ns0:v>
+        <ns0:v>2.1083147567126925</ns0:v>
       </ns0:c>
       <ns0:c r="I22">
-        <ns0:v>59.41999816894531</ns0:v>
+        <ns0:v>163.63999938964844</ns0:v>
       </ns0:c>
       <ns0:c r="J22">
-        <ns0:v>-0.16829094110163423</ns0:v>
+        <ns0:v>0.9227539186433598</ns0:v>
       </ns0:c>
       <ns0:c r="K22">
-        <ns0:v>0.5586065392643491</ns0:v>
+        <ns0:v>1.603410548555044</ns0:v>
       </ns0:c>
       <ns0:c r="L22">
-        <ns0:v>70.36057816788365</ns0:v>
+        <ns0:v>69.74409295494817</ns0:v>
       </ns0:c>
       <ns0:c r="M22">
-        <ns0:v>55.518999862670896</ns0:v>
+        <ns0:v>157.38149948120116</ns0:v>
       </ns0:c>
       <ns0:c r="N22">
-        <ns0:v>51.487999801635745</ns0:v>
+        <ns0:v>149.80099975585938</ns0:v>
       </ns0:c>
       <ns0:c r="O22">
-        <ns0:v>42.56194990158081</ns0:v>
+        <ns0:v>124.1611499786377</ns0:v>
       </ns0:c>
       <ns0:c r="P22" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q22" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </ns0:c>
       <ns0:c r="T22" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/DT/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/DAC/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1778,59 +1778,59 @@
       </ns0:c>
       <ns0:c r="B23" t="inlineStr">
         <ns0:is>
-          <ns0:t>ECO</ns0:t>
+          <ns0:t>DHT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C23" t="inlineStr">
         <ns0:is>
-          <ns0:t>Okeanis Eco Tankers Corp</ns0:t>
+          <ns0:t>DHT Holdings Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D23" t="inlineStr">
         <ns0:is>
-          <ns0:t>Industrials</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E23" t="inlineStr">
         <ns0:is>
-          <ns0:t>Marine Shipping</ns0:t>
+          <ns0:t>Oil &amp; Gas Midstream</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F23" t="inlineStr">
         <ns0:is>
-          <ns0:t>Okeanis Eco Tankers Corp., a shipping company, owns and operates tanker vessels worldwide. It operates a fleet of 16 tanker vessels comprising eight modern Suezmax tankers and eight modern VLCC tankers focusing on the transportation of crude oil. The company…</ns0:t>
+          <ns0:t>자회사를 통해 원유 운반선을 소유·운영하며 기술 관리 서비스도 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G23">
-        <ns0:v>87.27999877929688</ns0:v>
+        <ns0:v>23.68000030517578</ns0:v>
       </ns0:c>
       <ns0:c r="H23">
-        <ns0:v>1.7961289408640058</ns0:v>
+        <ns0:v>0.5093414344379266</ns0:v>
       </ns0:c>
       <ns0:c r="I23">
-        <ns0:v>87.30999755859375</ns0:v>
+        <ns0:v>23.610000610351562</ns0:v>
       </ns0:c>
       <ns0:c r="J23">
-        <ns0:v>-0.034358928113298326</ns0:v>
+        <ns0:v>0.29648324021442907</ns0:v>
       </ns0:c>
       <ns0:c r="K23">
-        <ns0:v>1.1351049781703533</ns0:v>
+        <ns0:v>0.8117970322541881</ns0:v>
       </ns0:c>
       <ns0:c r="L23">
-        <ns0:v>73.22743276170375</ns0:v>
+        <ns0:v>70.40390194239433</ns0:v>
       </ns0:c>
       <ns0:c r="M23">
-        <ns0:v>79.40999946594238</ns0:v>
+        <ns0:v>22.122500133514404</ns0:v>
       </ns0:c>
       <ns0:c r="N23">
-        <ns0:v>69.4485994720459</ns0:v>
+        <ns0:v>20.253200073242187</ns0:v>
       </ns0:c>
       <ns0:c r="O23">
-        <ns0:v>53.18334991455078</ns0:v>
+        <ns0:v>17.545400009155273</ns0:v>
       </ns0:c>
       <ns0:c r="P23" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q23" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </ns0:c>
       <ns0:c r="T23" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/ECO/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/DHT/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1857,59 +1857,59 @@
       </ns0:c>
       <ns0:c r="B24" t="inlineStr">
         <ns0:is>
-          <ns0:t>FBLA</ns0:t>
+          <ns0:t>DT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C24" t="inlineStr">
         <ns0:is>
-          <ns0:t>FB Bancorp Inc</ns0:t>
+          <ns0:t>Dynatrace Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D24" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E24" t="inlineStr">
         <ns0:is>
-          <ns0:t>Banks - Regional</ns0:t>
+          <ns0:t>Software - Application</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F24" t="inlineStr">
         <ns0:is>
-          <ns0:t>개인·기업·지역사회에 예금 등 은행 상품과 서비스를 제공하는 피델리티 은행의 지주회사.</ns0:t>
+          <ns0:t>디지털 기업의 복잡한 디지털 환경을 위한 AI 기반 관측성 플랫폼을 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G24">
-        <ns0:v>16.959999084472656</ns0:v>
+        <ns0:v>59.31999969482422</ns0:v>
       </ns0:c>
       <ns0:c r="H24">
-        <ns0:v>1.0726960099018523</ns0:v>
+        <ns0:v>0.1012510546582579</ns0:v>
       </ns0:c>
       <ns0:c r="I24">
-        <ns0:v>16.889999389648438</ns0:v>
+        <ns0:v>59.41999816894531</ns0:v>
       </ns0:c>
       <ns0:c r="J24">
-        <ns0:v>0.4144446261325596</ns0:v>
+        <ns0:v>-0.16829094110163423</ns0:v>
       </ns0:c>
       <ns0:c r="K24">
-        <ns0:v>0.6460650013430029</ns0:v>
+        <ns0:v>0.5586101618043727</ns0:v>
       </ns0:c>
       <ns0:c r="L24">
-        <ns0:v>71.67677110876173</ns0:v>
+        <ns0:v>70.36057816788365</ns0:v>
       </ns0:c>
       <ns0:c r="M24">
-        <ns0:v>16.247249937057497</ns0:v>
+        <ns0:v>55.518999862670896</ns0:v>
       </ns0:c>
       <ns0:c r="N24">
-        <ns0:v>15.899099960327149</ns0:v>
+        <ns0:v>51.487999801635745</ns0:v>
       </ns0:c>
       <ns0:c r="O24">
-        <ns0:v>14.32577501296997</ns0:v>
+        <ns0:v>42.56194990158081</ns0:v>
       </ns0:c>
       <ns0:c r="P24" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q24" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </ns0:c>
       <ns0:c r="T24" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/FBLA/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/DT/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -1936,55 +1936,55 @@
       </ns0:c>
       <ns0:c r="B25" t="inlineStr">
         <ns0:is>
-          <ns0:t>FOSL</ns0:t>
+          <ns0:t>ECO</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C25" t="inlineStr">
         <ns0:is>
-          <ns0:t>Fossil Group Inc</ns0:t>
+          <ns0:t>Okeanis Eco Tankers Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D25" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Industrials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E25" t="inlineStr">
         <ns0:is>
-          <ns0:t>Footwear &amp; Accessories</ns0:t>
+          <ns0:t>Marine Shipping</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F25" t="inlineStr">
         <ns0:is>
-          <ns0:t>시계·스마트워치·주얼리·핸드백·가죽 소품·벨트·선글라스 등 패션 액세서리를 설계·개발·유통.</ns0:t>
+          <ns0:t>Okeanis Eco Tankers Corp., a shipping company, owns and operates tanker vessels worldwide. It operates a fleet of 16 tanker vessels comprising eight modern Suezmax tankers and eight modern VLCC tankers focusing on the transportation of crude oil. The company…</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G25">
-        <ns0:v>6.800000190734863</ns0:v>
+        <ns0:v>87.27999877929688</ns0:v>
       </ns0:c>
       <ns0:c r="H25">
-        <ns0:v>0.0</ns0:v>
+        <ns0:v>1.7961289408640058</ns0:v>
       </ns0:c>
       <ns0:c r="I25">
-        <ns0:v>7.0</ns0:v>
+        <ns0:v>87.30999755859375</ns0:v>
       </ns0:c>
       <ns0:c r="J25">
-        <ns0:v>-2.857140132359093</ns0:v>
+        <ns0:v>-0.034358928113298326</ns0:v>
       </ns0:c>
       <ns0:c r="K25">
-        <ns0:v>1.3934608119387248</ns0:v>
+        <ns0:v>1.1352679897138453</ns0:v>
       </ns0:c>
       <ns0:c r="L25">
-        <ns0:v>68.08051821301893</ns0:v>
+        <ns0:v>73.22743276170375</ns0:v>
       </ns0:c>
       <ns0:c r="M25">
-        <ns0:v>5.68050000667572</ns0:v>
+        <ns0:v>79.40999946594238</ns0:v>
       </ns0:c>
       <ns0:c r="N25">
-        <ns0:v>5.4392000102996825</ns0:v>
+        <ns0:v>69.4485994720459</ns0:v>
       </ns0:c>
       <ns0:c r="O25">
-        <ns0:v>4.514000006914139</ns0:v>
+        <ns0:v>53.18334991455078</ns0:v>
       </ns0:c>
       <ns0:c r="P25" t="inlineStr">
         <ns0:is>
@@ -2003,7 +2003,7 @@
       </ns0:c>
       <ns0:c r="T25" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/FOSL/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/ECO/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2015,59 +2015,59 @@
       </ns0:c>
       <ns0:c r="B26" t="inlineStr">
         <ns0:is>
-          <ns0:t>FTNT</ns0:t>
+          <ns0:t>FBLA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C26" t="inlineStr">
         <ns0:is>
-          <ns0:t>Fortinet Inc</ns0:t>
+          <ns0:t>FB Bancorp Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D26" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E26" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Infrastructure</ns0:t>
+          <ns0:t>Banks - Regional</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F26" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에 사이버보안 및 네트워크·보안 통합 솔루션을 제공하는 기업.</ns0:t>
+          <ns0:t>개인·기업·지역사회에 예금 등 은행 상품과 서비스를 제공하는 피델리티 은행의 지주회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G26">
-        <ns0:v>180.9499969482422</ns0:v>
+        <ns0:v>16.959999084472656</ns0:v>
       </ns0:c>
       <ns0:c r="H26">
-        <ns0:v>1.247759463019027</ns0:v>
+        <ns0:v>1.0726960099018523</ns0:v>
       </ns0:c>
       <ns0:c r="I26">
-        <ns0:v>181.3699951171875</ns0:v>
+        <ns0:v>16.889999389648438</ns0:v>
       </ns0:c>
       <ns0:c r="J26">
-        <ns0:v>-0.23156981874203897</ns0:v>
+        <ns0:v>0.4144446261325596</ns0:v>
       </ns0:c>
       <ns0:c r="K26">
-        <ns0:v>0.8590553307705316</ns0:v>
+        <ns0:v>0.6464320888172621</ns0:v>
       </ns0:c>
       <ns0:c r="L26">
-        <ns0:v>64.1762999748936</ns0:v>
+        <ns0:v>71.67677110876173</ns0:v>
       </ns0:c>
       <ns0:c r="M26">
-        <ns0:v>170.68600006103514</ns0:v>
+        <ns0:v>16.247249937057497</ns0:v>
       </ns0:c>
       <ns0:c r="N26">
-        <ns0:v>163.64599975585938</ns0:v>
+        <ns0:v>15.899099960327149</ns0:v>
       </ns0:c>
       <ns0:c r="O26">
-        <ns0:v>118.57469982147217</ns0:v>
+        <ns0:v>14.32577501296997</ns0:v>
       </ns0:c>
       <ns0:c r="P26" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q26" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </ns0:c>
       <ns0:c r="T26" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/FTNT/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/FBLA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2094,59 +2094,59 @@
       </ns0:c>
       <ns0:c r="B27" t="inlineStr">
         <ns0:is>
-          <ns0:t>GIC</ns0:t>
+          <ns0:t>FOSL</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C27" t="inlineStr">
         <ns0:is>
-          <ns0:t>Global Industrial Co</ns0:t>
+          <ns0:t>Fossil Group Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D27" t="inlineStr">
         <ns0:is>
-          <ns0:t>Industrials</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E27" t="inlineStr">
         <ns0:is>
-          <ns0:t>Industrial Distribution</ns0:t>
+          <ns0:t>Footwear &amp; Accessories</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F27" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·캐나다에서 보관·선반·안전 제품 등 산업용 및 유지보수·수리·운영 용품을 유통하는 기업.</ns0:t>
+          <ns0:t>시계·스마트워치·주얼리·핸드백·가죽 소품·벨트·선글라스 등 패션 액세서리를 설계·개발·유통.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G27">
-        <ns0:v>43.61000061035156</ns0:v>
+        <ns0:v>6.800000190734863</ns0:v>
       </ns0:c>
       <ns0:c r="H27">
-        <ns0:v>1.2537750623486499</ns0:v>
+        <ns0:v>0.0</ns0:v>
       </ns0:c>
       <ns0:c r="I27">
-        <ns0:v>43.16999816894531</ns0:v>
+        <ns0:v>7.0</ns0:v>
       </ns0:c>
       <ns0:c r="J27">
-        <ns0:v>1.0192320131316768</ns0:v>
+        <ns0:v>-2.857140132359093</ns0:v>
       </ns0:c>
       <ns0:c r="K27">
-        <ns0:v>0.8034143920595533</ns0:v>
+        <ns0:v>1.393436964611822</ns0:v>
       </ns0:c>
       <ns0:c r="L27">
-        <ns0:v>75.04807865900221</ns0:v>
+        <ns0:v>68.08051821301893</ns0:v>
       </ns0:c>
       <ns0:c r="M27">
-        <ns0:v>40.837999725341795</ns0:v>
+        <ns0:v>5.68050000667572</ns0:v>
       </ns0:c>
       <ns0:c r="N27">
-        <ns0:v>39.338399734497074</ns0:v>
+        <ns0:v>5.4392000102996825</ns0:v>
       </ns0:c>
       <ns0:c r="O27">
-        <ns0:v>33.60509987831116</ns0:v>
+        <ns0:v>4.514000006914139</ns0:v>
       </ns0:c>
       <ns0:c r="P27" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q27" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </ns0:c>
       <ns0:c r="T27" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/GIC/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/FOSL/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2173,55 +2173,55 @@
       </ns0:c>
       <ns0:c r="B28" t="inlineStr">
         <ns0:is>
-          <ns0:t>GNE</ns0:t>
+          <ns0:t>FTNT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C28" t="inlineStr">
         <ns0:is>
-          <ns0:t>Genie Energy Ltd</ns0:t>
+          <ns0:t>Fortinet Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D28" t="inlineStr">
         <ns0:is>
-          <ns0:t>Utilities</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E28" t="inlineStr">
         <ns0:is>
-          <ns0:t>Utilities - Regulated Electric</ns0:t>
+          <ns0:t>Software - Infrastructure</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F28" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 및 해외에서 에너지 서비스를 제공하며 전력·천연가스 재판매와 재생에너지 사업을 영위.</ns0:t>
+          <ns0:t>전 세계에 사이버보안 및 네트워크·보안 통합 솔루션을 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G28">
-        <ns0:v>16.43000030517578</ns0:v>
+        <ns0:v>180.9499969482422</ns0:v>
       </ns0:c>
       <ns0:c r="H28">
-        <ns0:v>0.060902733467549375</ns0:v>
+        <ns0:v>1.247759463019027</ns0:v>
       </ns0:c>
       <ns0:c r="I28">
-        <ns0:v>16.549999237060547</ns0:v>
+        <ns0:v>181.3699951171875</ns0:v>
       </ns0:c>
       <ns0:c r="J28">
-        <ns0:v>-0.7250691082574257</ns0:v>
+        <ns0:v>-0.23156981874203897</ns0:v>
       </ns0:c>
       <ns0:c r="K28">
-        <ns0:v>0.878369384359401</ns0:v>
+        <ns0:v>0.8612730040057448</ns0:v>
       </ns0:c>
       <ns0:c r="L28">
-        <ns0:v>66.12337953572477</ns0:v>
+        <ns0:v>64.1762999748936</ns0:v>
       </ns0:c>
       <ns0:c r="M28">
-        <ns0:v>15.973000049591064</ns0:v>
+        <ns0:v>170.68600006103514</ns0:v>
       </ns0:c>
       <ns0:c r="N28">
-        <ns0:v>15.18379997253418</ns0:v>
+        <ns0:v>163.64599975585938</ns0:v>
       </ns0:c>
       <ns0:c r="O28">
-        <ns0:v>14.368349981307983</ns0:v>
+        <ns0:v>118.57469982147217</ns0:v>
       </ns0:c>
       <ns0:c r="P28" t="inlineStr">
         <ns0:is>
@@ -2240,7 +2240,7 @@
       </ns0:c>
       <ns0:c r="T28" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/GNE/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/FTNT/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2252,12 +2252,12 @@
       </ns0:c>
       <ns0:c r="B29" t="inlineStr">
         <ns0:is>
-          <ns0:t>HAFN</ns0:t>
+          <ns0:t>GIC</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C29" t="inlineStr">
         <ns0:is>
-          <ns0:t>Hafnia Ltd</ns0:t>
+          <ns0:t>Global Industrial Co</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D29" t="inlineStr">
@@ -2267,40 +2267,40 @@
       </ns0:c>
       <ns0:c r="E29" t="inlineStr">
         <ns0:is>
-          <ns0:t>Marine Shipping</ns0:t>
+          <ns0:t>Industrial Distribution</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F29" t="inlineStr">
         <ns0:is>
-          <ns0:t>석유제품 운반선을 보유·운영하며 정제 석유제품 등을 운송하는 버뮤다 투자지주회사.</ns0:t>
+          <ns0:t>미국·캐나다에서 보관·선반·안전 제품 등 산업용 및 유지보수·수리·운영 용품을 유통하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G29">
-        <ns0:v>10.25</ns0:v>
+        <ns0:v>43.61000061035156</ns0:v>
       </ns0:c>
       <ns0:c r="H29">
-        <ns0:v>1.787490671606462</ns0:v>
+        <ns0:v>1.2537750623486499</ns0:v>
       </ns0:c>
       <ns0:c r="I29">
-        <ns0:v>10.130000114440918</ns0:v>
+        <ns0:v>43.16999816894531</ns0:v>
       </ns0:c>
       <ns0:c r="J29">
-        <ns0:v>1.1845990543279061</ns0:v>
+        <ns0:v>1.0192320131316768</ns0:v>
       </ns0:c>
       <ns0:c r="K29">
-        <ns0:v>0.8062689534626238</ns0:v>
+        <ns0:v>0.8033085194375517</ns0:v>
       </ns0:c>
       <ns0:c r="L29">
-        <ns0:v>69.33416054245927</ns0:v>
+        <ns0:v>75.04807865900221</ns0:v>
       </ns0:c>
       <ns0:c r="M29">
-        <ns0:v>9.46899995803833</ns0:v>
+        <ns0:v>40.837999725341795</ns0:v>
       </ns0:c>
       <ns0:c r="N29">
-        <ns0:v>8.506599979400635</ns0:v>
+        <ns0:v>39.338399734497074</ns0:v>
       </ns0:c>
       <ns0:c r="O29">
-        <ns0:v>7.537699987888336</ns0:v>
+        <ns0:v>33.60509987831116</ns0:v>
       </ns0:c>
       <ns0:c r="P29" t="inlineStr">
         <ns0:is>
@@ -2319,7 +2319,7 @@
       </ns0:c>
       <ns0:c r="T29" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/HAFN/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/GIC/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2331,55 +2331,55 @@
       </ns0:c>
       <ns0:c r="B30" t="inlineStr">
         <ns0:is>
-          <ns0:t>HLP</ns0:t>
+          <ns0:t>GNE</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C30" t="inlineStr">
         <ns0:is>
-          <ns0:t>Hongli Group Inc</ns0:t>
+          <ns0:t>Genie Energy Ltd</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D30" t="inlineStr">
         <ns0:is>
-          <ns0:t>Basic Materials</ns0:t>
+          <ns0:t>Utilities</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E30" t="inlineStr">
         <ns0:is>
-          <ns0:t>Steel</ns0:t>
+          <ns0:t>Utilities - Regulated Electric</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F30" t="inlineStr">
         <ns0:is>
-          <ns0:t>중국과 해외에서 다양한 형태의 맞춤형 냉간 성형 강재를 제조·판매하는 회사.</ns0:t>
+          <ns0:t>미국 및 해외에서 에너지 서비스를 제공하며 전력·천연가스 재판매와 재생에너지 사업을 영위.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G30">
-        <ns0:v>2.549999952316284</ns0:v>
+        <ns0:v>16.43000030517578</ns0:v>
       </ns0:c>
       <ns0:c r="H30">
-        <ns0:v>0.3937004178520276</ns0:v>
+        <ns0:v>0.060902733467549375</ns0:v>
       </ns0:c>
       <ns0:c r="I30">
-        <ns0:v>2.609999895095825</ns0:v>
+        <ns0:v>16.549999237060547</ns0:v>
       </ns0:c>
       <ns0:c r="J30">
-        <ns0:v>-2.298848474755899</ns0:v>
+        <ns0:v>-0.7250691082574257</ns0:v>
       </ns0:c>
       <ns0:c r="K30">
-        <ns0:v>0.5284039808330262</ns0:v>
+        <ns0:v>0.8780238064763856</ns0:v>
       </ns0:c>
       <ns0:c r="L30">
-        <ns0:v>85.33899951271329</ns0:v>
+        <ns0:v>66.12337953572477</ns0:v>
       </ns0:c>
       <ns0:c r="M30">
-        <ns0:v>1.9445000052452088</ns0:v>
+        <ns0:v>15.973000049591064</ns0:v>
       </ns0:c>
       <ns0:c r="N30">
-        <ns0:v>1.5362999963760375</ns0:v>
+        <ns0:v>15.18379997253418</ns0:v>
       </ns0:c>
       <ns0:c r="O30">
-        <ns0:v>1.0499249954521657</ns0:v>
+        <ns0:v>14.368349981307983</ns0:v>
       </ns0:c>
       <ns0:c r="P30" t="inlineStr">
         <ns0:is>
@@ -2398,7 +2398,7 @@
       </ns0:c>
       <ns0:c r="T30" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/HLP/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/GNE/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2410,59 +2410,59 @@
       </ns0:c>
       <ns0:c r="B31" t="inlineStr">
         <ns0:is>
-          <ns0:t>HNGE</ns0:t>
+          <ns0:t>HAFN</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C31" t="inlineStr">
         <ns0:is>
-          <ns0:t>Hinge Health Inc</ns0:t>
+          <ns0:t>Hafnia Ltd</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D31" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Industrials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E31" t="inlineStr">
         <ns0:is>
-          <ns0:t>Health Information Services</ns0:t>
+          <ns0:t>Marine Shipping</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F31" t="inlineStr">
         <ns0:is>
-          <ns0:t>기술로 의료 제공을 확장·자동화하며 급성 부상·만성 통증·수술 후 재활 등 근골격계 관리 플랫폼을 개발하는 기업.</ns0:t>
+          <ns0:t>석유제품 운반선을 보유·운영하며 정제 석유제품 등을 운송하는 버뮤다 투자지주회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G31">
-        <ns0:v>97.66999816894531</ns0:v>
+        <ns0:v>10.25</ns0:v>
       </ns0:c>
       <ns0:c r="H31">
-        <ns0:v>-0.2756833425876959</ns0:v>
+        <ns0:v>1.787490671606462</ns0:v>
       </ns0:c>
       <ns0:c r="I31">
-        <ns0:v>98.45999908447266</ns0:v>
+        <ns0:v>10.130000114440918</ns0:v>
       </ns0:c>
       <ns0:c r="J31">
-        <ns0:v>-0.8023572241246613</ns0:v>
+        <ns0:v>1.1845990543279061</ns0:v>
       </ns0:c>
       <ns0:c r="K31">
-        <ns0:v>0.536790118012799</ns0:v>
+        <ns0:v>0.8063358549650809</ns0:v>
       </ns0:c>
       <ns0:c r="L31">
-        <ns0:v>60.9413306658102</ns0:v>
+        <ns0:v>69.33416054245927</ns0:v>
       </ns0:c>
       <ns0:c r="M31">
-        <ns0:v>93.6345001220703</ns0:v>
+        <ns0:v>9.46899995803833</ns0:v>
       </ns0:c>
       <ns0:c r="N31">
-        <ns0:v>88.5133999633789</ns0:v>
+        <ns0:v>8.506599979400635</ns0:v>
       </ns0:c>
       <ns0:c r="O31">
-        <ns0:v>61.15760003089905</ns0:v>
+        <ns0:v>7.537699987888336</ns0:v>
       </ns0:c>
       <ns0:c r="P31" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q31" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </ns0:c>
       <ns0:c r="T31" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/HNGE/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/HAFN/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2489,59 +2489,59 @@
       </ns0:c>
       <ns0:c r="B32" t="inlineStr">
         <ns0:is>
-          <ns0:t>IMOS</ns0:t>
+          <ns0:t>HLP</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C32" t="inlineStr">
         <ns0:is>
-          <ns0:t>Chipmos Technologies Inc ADR</ns0:t>
+          <ns0:t>Hongli Group Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D32" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Basic Materials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E32" t="inlineStr">
         <ns0:is>
-          <ns0:t>Semiconductors</ns0:t>
+          <ns0:t>Steel</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F32" t="inlineStr">
         <ns0:is>
-          <ns0:t>대만과 해외에서 집적회로 연구개발·제조·판매 및 관련 조립·검사 서비스를 제공하는 기업.</ns0:t>
+          <ns0:t>중국과 해외에서 다양한 형태의 맞춤형 냉간 성형 강재를 제조·판매하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G32">
-        <ns0:v>83.30000305175781</ns0:v>
+        <ns0:v>2.549999952316284</ns0:v>
       </ns0:c>
       <ns0:c r="H32">
-        <ns0:v>14.61200151622144</ns0:v>
+        <ns0:v>0.3937004178520276</ns0:v>
       </ns0:c>
       <ns0:c r="I32">
-        <ns0:v>78.3499984741211</ns0:v>
+        <ns0:v>2.609999895095825</ns0:v>
       </ns0:c>
       <ns0:c r="J32">
-        <ns0:v>6.3178106879883345</ns0:v>
+        <ns0:v>-2.298848474755899</ns0:v>
       </ns0:c>
       <ns0:c r="K32">
-        <ns0:v>3.036999117387467</ns0:v>
+        <ns0:v>0.5285661629192776</ns0:v>
       </ns0:c>
       <ns0:c r="L32">
-        <ns0:v>77.71610772233454</ns0:v>
+        <ns0:v>85.33899951271329</ns0:v>
       </ns0:c>
       <ns0:c r="M32">
-        <ns0:v>63.54700050354004</ns0:v>
+        <ns0:v>1.9445000052452088</ns0:v>
       </ns0:c>
       <ns0:c r="N32">
-        <ns0:v>57.77460006713867</ns0:v>
+        <ns0:v>1.5362999963760375</ns0:v>
       </ns0:c>
       <ns0:c r="O32">
-        <ns0:v>49.3321999168396</ns0:v>
+        <ns0:v>1.0499249954521657</ns0:v>
       </ns0:c>
       <ns0:c r="P32" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q32" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </ns0:c>
       <ns0:c r="T32" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/IMOS/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/HLP/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2568,59 +2568,59 @@
       </ns0:c>
       <ns0:c r="B33" t="inlineStr">
         <ns0:is>
-          <ns0:t>INSW</ns0:t>
+          <ns0:t>HNGE</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C33" t="inlineStr">
         <ns0:is>
-          <ns0:t>International Seaways Inc</ns0:t>
+          <ns0:t>Hinge Health Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D33" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E33" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas Midstream</ns0:t>
+          <ns0:t>Health Information Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F33" t="inlineStr">
         <ns0:is>
-          <ns0:t>원유와 석유제품의 국제 해상 운송을 위해 원유선과 제품 운반선을 보유·운영하는 기업.</ns0:t>
+          <ns0:t>기술로 의료 제공을 확장·자동화하며 급성 부상·만성 통증·수술 후 재활 등 근골격계 관리 플랫폼을 개발하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G33">
-        <ns0:v>115.80999755859375</ns0:v>
+        <ns0:v>97.66999816894531</ns0:v>
       </ns0:c>
       <ns0:c r="H33">
-        <ns0:v>1.055845637507491</ns0:v>
+        <ns0:v>-0.2756833425876959</ns0:v>
       </ns0:c>
       <ns0:c r="I33">
-        <ns0:v>114.79299926757812</ns0:v>
+        <ns0:v>98.45999908447266</ns0:v>
       </ns0:c>
       <ns0:c r="J33">
-        <ns0:v>0.8859410395271938</ns0:v>
+        <ns0:v>-0.8023572241246613</ns0:v>
       </ns0:c>
       <ns0:c r="K33">
-        <ns0:v>0.9552713023511207</ns0:v>
+        <ns0:v>0.5375893639655828</ns0:v>
       </ns0:c>
       <ns0:c r="L33">
-        <ns0:v>70.24803372116224</ns0:v>
+        <ns0:v>60.9413306658102</ns0:v>
       </ns0:c>
       <ns0:c r="M33">
-        <ns0:v>107.39799880981445</ns0:v>
+        <ns0:v>93.6345001220703</ns0:v>
       </ns0:c>
       <ns0:c r="N33">
-        <ns0:v>100.53859954833985</ns0:v>
+        <ns0:v>88.5133999633789</ns0:v>
       </ns0:c>
       <ns0:c r="O33">
-        <ns0:v>79.37519987106323</ns0:v>
+        <ns0:v>61.15760003089905</ns0:v>
       </ns0:c>
       <ns0:c r="P33" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q33" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </ns0:c>
       <ns0:c r="T33" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/INSW/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/HNGE/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2647,55 +2647,55 @@
       </ns0:c>
       <ns0:c r="B34" t="inlineStr">
         <ns0:is>
-          <ns0:t>JRSH</ns0:t>
+          <ns0:t>IMOS</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C34" t="inlineStr">
         <ns0:is>
-          <ns0:t>Jerash holdings (US) Inc</ns0:t>
+          <ns0:t>Chipmos Technologies Inc ADR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D34" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E34" t="inlineStr">
         <ns0:is>
-          <ns0:t>Apparel Manufacturing</ns0:t>
+          <ns0:t>Semiconductors</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F34" t="inlineStr">
         <ns0:is>
-          <ns0:t>편직물 기반 맞춤형 기성 스포츠웨어·겉옷과 개인보호장비를 제조·수출한다.</ns0:t>
+          <ns0:t>대만과 해외에서 집적회로 연구개발·제조·판매 및 관련 조립·검사 서비스를 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G34">
-        <ns0:v>6.150000095367432</ns0:v>
+        <ns0:v>83.30000305175781</ns0:v>
       </ns0:c>
       <ns0:c r="H34">
-        <ns0:v>5.488853788148207</ns0:v>
+        <ns0:v>14.61200151622144</ns0:v>
       </ns0:c>
       <ns0:c r="I34">
-        <ns0:v>5.96999979019165</ns0:v>
+        <ns0:v>78.3499984741211</ns0:v>
       </ns0:c>
       <ns0:c r="J34">
-        <ns0:v>3.015080594667885</ns0:v>
+        <ns0:v>6.3178106879883345</ns0:v>
       </ns0:c>
       <ns0:c r="K34">
-        <ns0:v>2.423681154104774</ns0:v>
+        <ns0:v>3.0397175639894085</ns0:v>
       </ns0:c>
       <ns0:c r="L34">
-        <ns0:v>67.56257728542386</ns0:v>
+        <ns0:v>77.71610772233454</ns0:v>
       </ns0:c>
       <ns0:c r="M34">
-        <ns0:v>5.588750004768372</ns0:v>
+        <ns0:v>63.54700050354004</ns0:v>
       </ns0:c>
       <ns0:c r="N34">
-        <ns0:v>5.345700006484986</ns0:v>
+        <ns0:v>57.77460006713867</ns0:v>
       </ns0:c>
       <ns0:c r="O34">
-        <ns0:v>3.9133999848365786</ns0:v>
+        <ns0:v>49.3321999168396</ns0:v>
       </ns0:c>
       <ns0:c r="P34" t="inlineStr">
         <ns0:is>
@@ -2714,7 +2714,7 @@
       </ns0:c>
       <ns0:c r="T34" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/JRSH/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/IMOS/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2726,55 +2726,55 @@
       </ns0:c>
       <ns0:c r="B35" t="inlineStr">
         <ns0:is>
-          <ns0:t>KEYS</ns0:t>
+          <ns0:t>INSW</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C35" t="inlineStr">
         <ns0:is>
-          <ns0:t>Keysight Technologies Inc</ns0:t>
+          <ns0:t>International Seaways Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D35" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E35" t="inlineStr">
         <ns0:is>
-          <ns0:t>Scientific &amp; Technical Instruments</ns0:t>
+          <ns0:t>Oil &amp; Gas Midstream</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F35" t="inlineStr">
         <ns0:is>
-          <ns0:t>전 세계에 전자 설계·시험용 소프트웨어, 계측기, 시스템 및 관련 서비스를 제공.</ns0:t>
+          <ns0:t>원유와 석유제품의 국제 해상 운송을 위해 원유선과 제품 운반선을 보유·운영하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G35">
-        <ns0:v>384.6400146484375</ns0:v>
+        <ns0:v>115.80999755859375</ns0:v>
       </ns0:c>
       <ns0:c r="H35">
-        <ns0:v>2.8779313215740343</ns0:v>
+        <ns0:v>1.055845637507491</ns0:v>
       </ns0:c>
       <ns0:c r="I35">
-        <ns0:v>376.67498779296875</ns0:v>
+        <ns0:v>114.79299926757812</ns0:v>
       </ns0:c>
       <ns0:c r="J35">
-        <ns0:v>2.114562185861546</ns0:v>
+        <ns0:v>0.8859410395271938</ns0:v>
       </ns0:c>
       <ns0:c r="K35">
-        <ns0:v>1.2111524055349623</ns0:v>
+        <ns0:v>0.9554235511406179</ns0:v>
       </ns0:c>
       <ns0:c r="L35">
-        <ns0:v>74.03973869727929</ns0:v>
+        <ns0:v>70.24803372116224</ns0:v>
       </ns0:c>
       <ns0:c r="M35">
-        <ns0:v>343.9040008544922</ns0:v>
+        <ns0:v>107.39799880981445</ns0:v>
       </ns0:c>
       <ns0:c r="N35">
-        <ns0:v>334.1060009765625</ns0:v>
+        <ns0:v>100.53859954833985</ns0:v>
       </ns0:c>
       <ns0:c r="O35">
-        <ns0:v>302.5307992553711</ns0:v>
+        <ns0:v>79.37519987106323</ns0:v>
       </ns0:c>
       <ns0:c r="P35" t="inlineStr">
         <ns0:is>
@@ -2793,7 +2793,7 @@
       </ns0:c>
       <ns0:c r="T35" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/KEYS/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/INSW/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2805,12 +2805,12 @@
       </ns0:c>
       <ns0:c r="B36" t="inlineStr">
         <ns0:is>
-          <ns0:t>KRT</ns0:t>
+          <ns0:t>JILL</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C36" t="inlineStr">
         <ns0:is>
-          <ns0:t>Karat Packaging Inc</ns0:t>
+          <ns0:t>J.Jill Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D36" t="inlineStr">
@@ -2820,40 +2820,40 @@
       </ns0:c>
       <ns0:c r="E36" t="inlineStr">
         <ns0:is>
-          <ns0:t>Packaging &amp; Containers</ns0:t>
+          <ns0:t>Apparel Retail</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F36" t="inlineStr">
         <ns0:is>
-          <ns0:t>외식업용 플라스틱·종이·바이오폴리머·퇴비화 소재 일회용 용기와 포장재를 제조·유통하는 기업.</ns0:t>
+          <ns0:t>미국에서 온·오프라인 채널을 통해 여성 의류·신발·장신구·가방 등 패션 상품을 판매한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G36">
-        <ns0:v>54.56999969482422</ns0:v>
+        <ns0:v>24.84000015258789</ns0:v>
       </ns0:c>
       <ns0:c r="H36">
-        <ns0:v>2.2484556622738516</ns0:v>
+        <ns0:v>1.803280905477811</ns0:v>
       </ns0:c>
       <ns0:c r="I36">
-        <ns0:v>54.665000915527344</ns0:v>
+        <ns0:v>25.0</ns0:v>
       </ns0:c>
       <ns0:c r="J36">
-        <ns0:v>-0.17378801630302254</ns0:v>
+        <ns0:v>-0.6399993896484379</ns0:v>
       </ns0:c>
       <ns0:c r="K36">
-        <ns0:v>1.4053643071570856</ns0:v>
+        <ns0:v>1.0732805402580696</ns0:v>
       </ns0:c>
       <ns0:c r="L36">
-        <ns0:v>72.1361579520966</ns0:v>
+        <ns0:v>72.0550498535534</ns0:v>
       </ns0:c>
       <ns0:c r="M36">
-        <ns0:v>50.76499977111816</ns0:v>
+        <ns0:v>23.5729998588562</ns0:v>
       </ns0:c>
       <ns0:c r="N36">
-        <ns0:v>47.789599914550784</ns0:v>
+        <ns0:v>20.87499988555908</ns0:v>
       </ns0:c>
       <ns0:c r="O36">
-        <ns0:v>32.69335000038147</ns0:v>
+        <ns0:v>16.213650012016295</ns0:v>
       </ns0:c>
       <ns0:c r="P36" t="inlineStr">
         <ns0:is>
@@ -2872,7 +2872,7 @@
       </ns0:c>
       <ns0:c r="T36" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/KRT/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/JILL/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2884,12 +2884,12 @@
       </ns0:c>
       <ns0:c r="B37" t="inlineStr">
         <ns0:is>
-          <ns0:t>LIND</ns0:t>
+          <ns0:t>JRSH</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C37" t="inlineStr">
         <ns0:is>
-          <ns0:t>Lindblad Expeditions Holdings Inc</ns0:t>
+          <ns0:t>Jerash holdings (US) Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D37" t="inlineStr">
@@ -2899,44 +2899,44 @@
       </ns0:c>
       <ns0:c r="E37" t="inlineStr">
         <ns0:is>
-          <ns0:t>Travel Services</ns0:t>
+          <ns0:t>Apparel Manufacturing</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F37" t="inlineStr">
         <ns0:is>
-          <ns0:t>맞춤형 선박을 활용한 해양 탐험과 육상 여행 체험을 전 세계에 제공하는 기업.</ns0:t>
+          <ns0:t>편직물 기반 맞춤형 기성 스포츠웨어·겉옷과 개인보호장비를 제조·수출한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G37">
-        <ns0:v>34.779998779296875</ns0:v>
+        <ns0:v>6.150000095367432</ns0:v>
       </ns0:c>
       <ns0:c r="H37">
-        <ns0:v>3.419558949321466</ns0:v>
+        <ns0:v>5.488853788148207</ns0:v>
       </ns0:c>
       <ns0:c r="I37">
-        <ns0:v>35.0</ns0:v>
+        <ns0:v>5.96999979019165</ns0:v>
       </ns0:c>
       <ns0:c r="J37">
-        <ns0:v>-0.6285749162946441</ns0:v>
+        <ns0:v>3.015080594667885</ns0:v>
       </ns0:c>
       <ns0:c r="K37">
-        <ns0:v>1.1001420104067858</ns0:v>
+        <ns0:v>2.4231309982272755</ns0:v>
       </ns0:c>
       <ns0:c r="L37">
-        <ns0:v>76.1123982434018</ns0:v>
+        <ns0:v>67.56257728542386</ns0:v>
       </ns0:c>
       <ns0:c r="M37">
-        <ns0:v>28.156500148773194</ns0:v>
+        <ns0:v>5.588750004768372</ns0:v>
       </ns0:c>
       <ns0:c r="N37">
-        <ns0:v>29.83660011291504</ns0:v>
+        <ns0:v>5.345700006484986</ns0:v>
       </ns0:c>
       <ns0:c r="O37">
-        <ns0:v>22.35679997444153</ns0:v>
+        <ns0:v>3.9133999848365786</ns0:v>
       </ns0:c>
       <ns0:c r="P37" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q37" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </ns0:c>
       <ns0:c r="T37" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/LIND/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/JRSH/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -2963,12 +2963,12 @@
       </ns0:c>
       <ns0:c r="B38" t="inlineStr">
         <ns0:is>
-          <ns0:t>LITE</ns0:t>
+          <ns0:t>KEYS</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C38" t="inlineStr">
         <ns0:is>
-          <ns0:t>Lumentum Holdings Inc</ns0:t>
+          <ns0:t>Keysight Technologies Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D38" t="inlineStr">
@@ -2978,44 +2978,44 @@
       </ns0:c>
       <ns0:c r="E38" t="inlineStr">
         <ns0:is>
-          <ns0:t>Communication Equipment</ns0:t>
+          <ns0:t>Scientific &amp; Technical Instruments</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F38" t="inlineStr">
         <ns0:is>
-          <ns0:t>반도체 레이저 칩, 레이저 부품, 파장 관리 시스템 등 광학·광자 제품을 제조·판매하는 기업.</ns0:t>
+          <ns0:t>전 세계에 전자 설계·시험용 소프트웨어, 계측기, 시스템 및 관련 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G38">
-        <ns0:v>1085.4200439453125</ns0:v>
+        <ns0:v>384.6400146484375</ns0:v>
       </ns0:c>
       <ns0:c r="H38">
-        <ns0:v>3.790473477973122</ns0:v>
+        <ns0:v>2.8779313215740343</ns0:v>
       </ns0:c>
       <ns0:c r="I38">
-        <ns0:v>1085.6800537109375</ns0:v>
+        <ns0:v>376.67498779296875</ns0:v>
       </ns0:c>
       <ns0:c r="J38">
-        <ns0:v>-0.023949022986680113</ns0:v>
+        <ns0:v>2.114562185861546</ns0:v>
       </ns0:c>
       <ns0:c r="K38">
-        <ns0:v>0.9666667703012346</ns0:v>
+        <ns0:v>1.2178081394220506</ns0:v>
       </ns0:c>
       <ns0:c r="L38">
-        <ns0:v>66.67582507350136</ns0:v>
+        <ns0:v>74.03973869727929</ns0:v>
       </ns0:c>
       <ns0:c r="M38">
-        <ns0:v>941.7265045166016</ns0:v>
+        <ns0:v>343.9040008544922</ns0:v>
       </ns0:c>
       <ns0:c r="N38">
-        <ns0:v>879.0255029296875</ns0:v>
+        <ns0:v>334.1060009765625</ns0:v>
       </ns0:c>
       <ns0:c r="O38">
-        <ns0:v>745.4280258178711</ns0:v>
+        <ns0:v>302.5307992553711</ns0:v>
       </ns0:c>
       <ns0:c r="P38" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q38" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </ns0:c>
       <ns0:c r="T38" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/LITE/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/KEYS/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3042,12 +3042,12 @@
       </ns0:c>
       <ns0:c r="B39" t="inlineStr">
         <ns0:is>
-          <ns0:t>LQDT</ns0:t>
+          <ns0:t>KRT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C39" t="inlineStr">
         <ns0:is>
-          <ns0:t>Liquidity Services Inc</ns0:t>
+          <ns0:t>Karat Packaging Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D39" t="inlineStr">
@@ -3057,40 +3057,40 @@
       </ns0:c>
       <ns0:c r="E39" t="inlineStr">
         <ns0:is>
-          <ns0:t>Internet Retail</ns0:t>
+          <ns0:t>Packaging &amp; Containers</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F39" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 전자상거래 장터, 직접 경매 등록 도구 및 부가 서비스를 제공하는 회사.</ns0:t>
+          <ns0:t>외식업용 플라스틱·종이·바이오폴리머·퇴비화 소재 일회용 용기와 포장재를 제조·유통하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G39">
-        <ns0:v>43.22999954223633</ns0:v>
+        <ns0:v>54.56999969482422</ns0:v>
       </ns0:c>
       <ns0:c r="H39">
-        <ns0:v>-0.9395047047350835</ns0:v>
+        <ns0:v>2.2484556622738516</ns0:v>
       </ns0:c>
       <ns0:c r="I39">
-        <ns0:v>44.529998779296875</ns0:v>
+        <ns0:v>54.665000915527344</ns0:v>
       </ns0:c>
       <ns0:c r="J39">
-        <ns0:v>-2.9193785598416677</ns0:v>
+        <ns0:v>-0.17378801630302254</ns0:v>
       </ns0:c>
       <ns0:c r="K39">
-        <ns0:v>1.6233478260869565</ns0:v>
+        <ns0:v>1.4056055887551553</ns0:v>
       </ns0:c>
       <ns0:c r="L39">
-        <ns0:v>55.585219952478774</ns0:v>
+        <ns0:v>72.1361579520966</ns0:v>
       </ns0:c>
       <ns0:c r="M39">
-        <ns0:v>42.83000087738037</ns0:v>
+        <ns0:v>50.76499977111816</ns0:v>
       </ns0:c>
       <ns0:c r="N39">
-        <ns0:v>41.7478003692627</ns0:v>
+        <ns0:v>47.789599914550784</ns0:v>
       </ns0:c>
       <ns0:c r="O39">
-        <ns0:v>35.72135008811951</ns0:v>
+        <ns0:v>32.69335000038147</ns0:v>
       </ns0:c>
       <ns0:c r="P39" t="inlineStr">
         <ns0:is>
@@ -3109,7 +3109,7 @@
       </ns0:c>
       <ns0:c r="T39" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/LQDT/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/KRT/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3121,59 +3121,59 @@
       </ns0:c>
       <ns0:c r="B40" t="inlineStr">
         <ns0:is>
-          <ns0:t>MTRN</ns0:t>
+          <ns0:t>LIND</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C40" t="inlineStr">
         <ns0:is>
-          <ns0:t>Materion Corp</ns0:t>
+          <ns0:t>Lindblad Expeditions Holdings Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D40" t="inlineStr">
         <ns0:is>
-          <ns0:t>Basic Materials</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E40" t="inlineStr">
         <ns0:is>
-          <ns0:t>Other Industrial Metals &amp; Mining</ns0:t>
+          <ns0:t>Travel Services</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F40" t="inlineStr">
         <ns0:is>
-          <ns0:t>베릴륨 함유·비함유 합금 등 첨단 소재를 생산하며 전자재료와 정밀광학 사업을 운영하는 기업.</ns0:t>
+          <ns0:t>맞춤형 선박을 활용한 해양 탐험과 육상 여행 체험을 전 세계에 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G40">
-        <ns0:v>312.1600036621094</ns0:v>
+        <ns0:v>34.779998779296875</ns0:v>
       </ns0:c>
       <ns0:c r="H40">
-        <ns0:v>9.476042514406856</ns0:v>
+        <ns0:v>3.419558949321466</ns0:v>
       </ns0:c>
       <ns0:c r="I40">
-        <ns0:v>304.5799865722656</ns0:v>
+        <ns0:v>35.0</ns0:v>
       </ns0:c>
       <ns0:c r="J40">
-        <ns0:v>2.4886786473231615</ns0:v>
+        <ns0:v>-0.6285749162946441</ns0:v>
       </ns0:c>
       <ns0:c r="K40">
-        <ns0:v>1.6173044991697842</ns0:v>
+        <ns0:v>1.1002242558161213</ns0:v>
       </ns0:c>
       <ns0:c r="L40">
-        <ns0:v>77.41974887911535</ns0:v>
+        <ns0:v>76.1123982434018</ns0:v>
       </ns0:c>
       <ns0:c r="M40">
-        <ns0:v>258.6695014953613</ns0:v>
+        <ns0:v>28.156500148773194</ns0:v>
       </ns0:c>
       <ns0:c r="N40">
-        <ns0:v>251.64940093994142</ns0:v>
+        <ns0:v>29.83660011291504</ns0:v>
       </ns0:c>
       <ns0:c r="O40">
-        <ns0:v>199.42779949188233</ns0:v>
+        <ns0:v>22.35679997444153</ns0:v>
       </ns0:c>
       <ns0:c r="P40" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q40" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </ns0:c>
       <ns0:c r="T40" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/MTRN/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/LIND/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3200,59 +3200,59 @@
       </ns0:c>
       <ns0:c r="B41" t="inlineStr">
         <ns0:is>
-          <ns0:t>NAT</ns0:t>
+          <ns0:t>LITE</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C41" t="inlineStr">
         <ns0:is>
-          <ns0:t>Nordic American Tankers Ltd</ns0:t>
+          <ns0:t>Lumentum Holdings Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D41" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E41" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas Midstream</ns0:t>
+          <ns0:t>Communication Equipment</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F41" t="inlineStr">
         <ns0:is>
-          <ns0:t>버뮤다와 해외에서 이중선체 유조선을 보유·운영·용선하며 석유회사와 원유 거래업체에 서비스를 제공.</ns0:t>
+          <ns0:t>반도체 레이저 칩, 레이저 부품, 파장 관리 시스템 등 광학·광자 제품을 제조·판매하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G41">
-        <ns0:v>8.420000076293945</ns0:v>
+        <ns0:v>1085.4200439453125</ns0:v>
       </ns0:c>
       <ns0:c r="H41">
-        <ns0:v>3.0599754916208477</ns0:v>
+        <ns0:v>3.790473477973122</ns0:v>
       </ns0:c>
       <ns0:c r="I41">
-        <ns0:v>8.329999923706055</ns0:v>
+        <ns0:v>1085.6800537109375</ns0:v>
       </ns0:c>
       <ns0:c r="J41">
-        <ns0:v>1.0804340145521785</ns0:v>
+        <ns0:v>-0.023949022986680113</ns0:v>
       </ns0:c>
       <ns0:c r="K41">
-        <ns0:v>0.9705895858711945</ns0:v>
+        <ns0:v>0.9680504990522619</ns0:v>
       </ns0:c>
       <ns0:c r="L41">
-        <ns0:v>71.45859113740819</ns0:v>
+        <ns0:v>66.67582507350136</ns0:v>
       </ns0:c>
       <ns0:c r="M41">
-        <ns0:v>7.755999946594239</ns0:v>
+        <ns0:v>941.7265045166016</ns0:v>
       </ns0:c>
       <ns0:c r="N41">
-        <ns0:v>7.089999980926514</ns0:v>
+        <ns0:v>879.0255029296875</ns0:v>
       </ns0:c>
       <ns0:c r="O41">
-        <ns0:v>5.645849994421005</ns0:v>
+        <ns0:v>745.4280258178711</ns0:v>
       </ns0:c>
       <ns0:c r="P41" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q41" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </ns0:c>
       <ns0:c r="T41" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/NAT/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/LITE/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3279,59 +3279,59 @@
       </ns0:c>
       <ns0:c r="B42" t="inlineStr">
         <ns0:is>
-          <ns0:t>NNBR</ns0:t>
+          <ns0:t>LQDT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C42" t="inlineStr">
         <ns0:is>
-          <ns0:t>NN Inc</ns0:t>
+          <ns0:t>Liquidity Services Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D42" t="inlineStr">
         <ns0:is>
-          <ns0:t>Industrials</ns0:t>
+          <ns0:t>Consumer Cyclical</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E42" t="inlineStr">
         <ns0:is>
-          <ns0:t>Conglomerates</ns0:t>
+          <ns0:t>Internet Retail</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F42" t="inlineStr">
         <ns0:is>
-          <ns0:t>모빌리티·전력 솔루션 부문을 통해 다양한 산업용 고정밀 부품과 조립품을 설계·제조·판매하는 기업.</ns0:t>
+          <ns0:t>미국과 해외에서 전자상거래 장터, 직접 경매 등록 도구 및 부가 서비스를 제공하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G42">
-        <ns0:v>4.510000228881836</ns0:v>
+        <ns0:v>43.22999954223633</ns0:v>
       </ns0:c>
       <ns0:c r="H42">
-        <ns0:v>24.242426630789595</ns0:v>
+        <ns0:v>-0.9395047047350835</ns0:v>
       </ns0:c>
       <ns0:c r="I42">
-        <ns0:v>4.480000019073486</ns0:v>
+        <ns0:v>44.529998779296875</ns0:v>
       </ns0:c>
       <ns0:c r="J42">
-        <ns0:v>0.6696475375139288</ns0:v>
+        <ns0:v>-2.9193785598416677</ns0:v>
       </ns0:c>
       <ns0:c r="K42">
-        <ns0:v>7.24336736207971</ns0:v>
+        <ns0:v>1.6234782608695653</ns0:v>
       </ns0:c>
       <ns0:c r="L42">
-        <ns0:v>68.89239374372428</ns0:v>
+        <ns0:v>55.585219952478774</ns0:v>
       </ns0:c>
       <ns0:c r="M42">
-        <ns0:v>3.60900000333786</ns0:v>
+        <ns0:v>42.83000087738037</ns0:v>
       </ns0:c>
       <ns0:c r="N42">
-        <ns0:v>3.607400002479553</ns0:v>
+        <ns0:v>41.7478003692627</ns0:v>
       </ns0:c>
       <ns0:c r="O42">
-        <ns0:v>2.4748500031232834</ns0:v>
+        <ns0:v>35.72135008811951</ns0:v>
       </ns0:c>
       <ns0:c r="P42" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q42" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </ns0:c>
       <ns0:c r="T42" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/NNBR/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/LQDT/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3358,56 +3358,59 @@
       </ns0:c>
       <ns0:c r="B43" t="inlineStr">
         <ns0:is>
-          <ns0:t>NPAC</ns0:t>
+          <ns0:t>MSM</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C43" t="inlineStr">
         <ns0:is>
-          <ns0:t>New Providence Acquisition Corp III</ns0:t>
+          <ns0:t>MSC Industrial Direct Co Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D43" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Industrials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E43" t="inlineStr">
         <ns0:is>
-          <ns0:t>Shell Companies</ns0:t>
+          <ns0:t>Industrial Distribution</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F43" t="inlineStr">
         <ns0:is>
-          <ns0:t>주요 영업활동 없이 기업 합병, 주식 교환, 자산 인수 등 기업결합을 추진한다.</ns0:t>
+          <ns0:t>미국·캐나다·멕시코·영국 등에서 금속가공 및 유지보수·수리·운영용 제품과 서비스를 유통한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G43">
-        <ns0:v>10.539999961853027</ns0:v>
+        <ns0:v>130.1199951171875</ns0:v>
       </ns0:c>
       <ns0:c r="H43">
-        <ns0:v>0.09496893765841286</ns0:v>
+        <ns0:v>1.2606965892509647</ns0:v>
       </ns0:c>
       <ns0:c r="I43">
-        <ns0:v>10.529999732971191</ns0:v>
+        <ns0:v>130.4600067138672</ns0:v>
       </ns0:c>
       <ns0:c r="J43">
-        <ns0:v>0.09496893765841286</ns0:v>
+        <ns0:v>-0.2606251565090201</ns0:v>
+      </ns0:c>
+      <ns0:c r="K43">
+        <ns0:v>1.0862767958875434</ns0:v>
       </ns0:c>
       <ns0:c r="L43">
-        <ns0:v>75.95293098823926</ns0:v>
+        <ns0:v>68.30624372177016</ns0:v>
       </ns0:c>
       <ns0:c r="M43">
-        <ns0:v>10.48984990119934</ns0:v>
+        <ns0:v>122.15500030517578</ns0:v>
       </ns0:c>
       <ns0:c r="N43">
-        <ns0:v>10.463039932250977</ns0:v>
+        <ns0:v>121.89699996948242</ns0:v>
       </ns0:c>
       <ns0:c r="O43">
-        <ns0:v>10.356289982795715</ns0:v>
+        <ns0:v>105.32605003356933</ns0:v>
       </ns0:c>
       <ns0:c r="P43" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q43" t="inlineStr">
@@ -3422,7 +3425,7 @@
       </ns0:c>
       <ns0:c r="T43" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/NPAC/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/MSM/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3434,55 +3437,55 @@
       </ns0:c>
       <ns0:c r="B44" t="inlineStr">
         <ns0:is>
-          <ns0:t>NTAP</ns0:t>
+          <ns0:t>MTRN</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C44" t="inlineStr">
         <ns0:is>
-          <ns0:t>Netapp Inc</ns0:t>
+          <ns0:t>Materion Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D44" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Basic Materials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E44" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Infrastructure</ns0:t>
+          <ns0:t>Other Industrial Metals &amp; Mining</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F44" t="inlineStr">
         <ns0:is>
-          <ns0:t>하이브리드·퍼블릭 클라우드 부문에서 데이터 인프라용 기업 소프트웨어·시스템·서비스를 개발하는 기업.</ns0:t>
+          <ns0:t>베릴륨 함유·비함유 합금 등 첨단 소재를 생산하며 전자재료와 정밀광학 사업을 운영하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G44">
-        <ns0:v>226.27000427246094</ns0:v>
+        <ns0:v>312.1600036621094</ns0:v>
       </ns0:c>
       <ns0:c r="H44">
-        <ns0:v>5.2173917979451145</ns0:v>
+        <ns0:v>9.476042514406856</ns0:v>
       </ns0:c>
       <ns0:c r="I44">
-        <ns0:v>216.80999755859375</ns0:v>
+        <ns0:v>304.5799865722656</ns0:v>
       </ns0:c>
       <ns0:c r="J44">
-        <ns0:v>4.3632705227583335</ns0:v>
+        <ns0:v>2.4886786473231615</ns0:v>
       </ns0:c>
       <ns0:c r="K44">
-        <ns0:v>1.847478244268117</ns0:v>
+        <ns0:v>1.6296237021625624</ns0:v>
       </ns0:c>
       <ns0:c r="L44">
-        <ns0:v>75.92517280506357</ns0:v>
+        <ns0:v>77.41974887911535</ns0:v>
       </ns0:c>
       <ns0:c r="M44">
-        <ns0:v>197.87600021362306</ns0:v>
+        <ns0:v>258.6695014953613</ns0:v>
       </ns0:c>
       <ns0:c r="N44">
-        <ns0:v>192.3292007446289</ns0:v>
+        <ns0:v>251.64940093994142</ns0:v>
       </ns0:c>
       <ns0:c r="O44">
-        <ns0:v>138.75979988098143</ns0:v>
+        <ns0:v>199.42779949188233</ns0:v>
       </ns0:c>
       <ns0:c r="P44" t="inlineStr">
         <ns0:is>
@@ -3501,7 +3504,7 @@
       </ns0:c>
       <ns0:c r="T44" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/NTAP/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/MTRN/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3513,55 +3516,55 @@
       </ns0:c>
       <ns0:c r="B45" t="inlineStr">
         <ns0:is>
-          <ns0:t>NTWK</ns0:t>
+          <ns0:t>MTW</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C45" t="inlineStr">
         <ns0:is>
-          <ns0:t>Netsol Technologies Inc</ns0:t>
+          <ns0:t>Manitowoc Co Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D45" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Industrials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E45" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Application</ns0:t>
+          <ns0:t>Farm &amp; Heavy Construction Machinery</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F45" t="inlineStr">
         <ns0:is>
-          <ns0:t>자동차 금융·리스, 은행 및 금융서비스 산업용 기업 소프트웨어를 설계·개발·판매하는 회사.</ns0:t>
+          <ns0:t>전 세계에 중량물 인양 솔루션을 제공하고 크롤러형 격자 붐 크레인 등을 설계·제조·유통한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G45">
-        <ns0:v>5.949999809265137</ns0:v>
+        <ns0:v>23.219999313354492</ns0:v>
       </ns0:c>
       <ns0:c r="H45">
-        <ns0:v>3.4782575524371584</ns0:v>
+        <ns0:v>3.660712985663972</ns0:v>
       </ns0:c>
       <ns0:c r="I45">
-        <ns0:v>5.869999885559082</ns0:v>
+        <ns0:v>23.170000076293945</ns0:v>
       </ns0:c>
       <ns0:c r="J45">
-        <ns0:v>1.3628607370651524</ns0:v>
+        <ns0:v>0.21579299480323222</ns0:v>
       </ns0:c>
       <ns0:c r="K45">
-        <ns0:v>1.5151288833566723</ns0:v>
+        <ns0:v>0.7623898374758119</ns0:v>
       </ns0:c>
       <ns0:c r="L45">
-        <ns0:v>85.15649476886331</ns0:v>
+        <ns0:v>66.33500173502162</ns0:v>
       </ns0:c>
       <ns0:c r="M45">
-        <ns0:v>4.637499976158142</ns0:v>
+        <ns0:v>21.667499923706053</ns0:v>
       </ns0:c>
       <ns0:c r="N45">
-        <ns0:v>4.358200025558472</ns0:v>
+        <ns0:v>19.361599979400633</ns0:v>
       </ns0:c>
       <ns0:c r="O45">
-        <ns0:v>3.882200005054474</ns0:v>
+        <ns0:v>14.600700016021728</ns0:v>
       </ns0:c>
       <ns0:c r="P45" t="inlineStr">
         <ns0:is>
@@ -3580,7 +3583,7 @@
       </ns0:c>
       <ns0:c r="T45" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/NTWK/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/MTW/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3592,59 +3595,59 @@
       </ns0:c>
       <ns0:c r="B46" t="inlineStr">
         <ns0:is>
-          <ns0:t>NVDA</ns0:t>
+          <ns0:t>NAT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C46" t="inlineStr">
         <ns0:is>
-          <ns0:t>NVIDIA Corp</ns0:t>
+          <ns0:t>Nordic American Tankers Ltd</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D46" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E46" t="inlineStr">
         <ns0:is>
-          <ns0:t>Semiconductors</ns0:t>
+          <ns0:t>Oil &amp; Gas Midstream</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F46" t="inlineStr">
         <ns0:is>
-          <ns0:t>컴퓨팅·네트워킹 및 그래픽 부문을 운영하는 데이터센터 규모의 AI 인프라 기업.</ns0:t>
+          <ns0:t>버뮤다와 해외에서 이중선체 유조선을 보유·운영·용선하며 석유회사와 원유 거래업체에 서비스를 제공.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G46">
-        <ns0:v>233.9499969482422</ns0:v>
+        <ns0:v>8.420000076293945</ns0:v>
       </ns0:c>
       <ns0:c r="H46">
-        <ns0:v>1.3384719439145876</ns0:v>
+        <ns0:v>3.0599754916208477</ns0:v>
       </ns0:c>
       <ns0:c r="I46">
-        <ns0:v>236.5399932861328</ns0:v>
+        <ns0:v>8.329999923706055</ns0:v>
       </ns0:c>
       <ns0:c r="J46">
-        <ns0:v>-1.0949507108329093</ns0:v>
+        <ns0:v>1.0804340145521785</ns0:v>
       </ns0:c>
       <ns0:c r="K46">
-        <ns0:v>1.2231092958450822</ns0:v>
+        <ns0:v>0.9737365838008011</ns0:v>
       </ns0:c>
       <ns0:c r="L46">
-        <ns0:v>62.897434590233345</ns0:v>
+        <ns0:v>71.45859113740819</ns0:v>
       </ns0:c>
       <ns0:c r="M46">
-        <ns0:v>223.78600006103517</ns0:v>
+        <ns0:v>7.755999946594239</ns0:v>
       </ns0:c>
       <ns0:c r="N46">
-        <ns0:v>218.27820007324217</ns0:v>
+        <ns0:v>7.089999980926514</ns0:v>
       </ns0:c>
       <ns0:c r="O46">
-        <ns0:v>200.71460006713866</ns0:v>
+        <ns0:v>5.645849994421005</ns0:v>
       </ns0:c>
       <ns0:c r="P46" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q46" t="inlineStr">
@@ -3659,7 +3662,7 @@
       </ns0:c>
       <ns0:c r="T46" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/NVDA/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/NAT/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3671,59 +3674,59 @@
       </ns0:c>
       <ns0:c r="B47" t="inlineStr">
         <ns0:is>
-          <ns0:t>OKTA</ns0:t>
+          <ns0:t>NNBR</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C47" t="inlineStr">
         <ns0:is>
-          <ns0:t>Okta Inc</ns0:t>
+          <ns0:t>NN Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D47" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Industrials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E47" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Infrastructure</ns0:t>
+          <ns0:t>Conglomerates</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F47" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국과 해외에서 싱글 사인온과 위험 기반 다중요소 인증 등 신원·접근 보안 서비스를 제공하는 회사.</ns0:t>
+          <ns0:t>모빌리티·전력 솔루션 부문을 통해 다양한 산업용 고정밀 부품과 조립품을 설계·제조·판매하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G47">
-        <ns0:v>211.49000549316406</ns0:v>
+        <ns0:v>4.510000228881836</ns0:v>
       </ns0:c>
       <ns0:c r="H47">
-        <ns0:v>-0.5361422957577133</ns0:v>
+        <ns0:v>24.242426630789595</ns0:v>
       </ns0:c>
       <ns0:c r="I47">
-        <ns0:v>213.86000061035156</ns0:v>
+        <ns0:v>4.480000019073486</ns0:v>
       </ns0:c>
       <ns0:c r="J47">
-        <ns0:v>-1.1081993408882385</ns0:v>
+        <ns0:v>0.6696475375139288</ns0:v>
       </ns0:c>
       <ns0:c r="K47">
-        <ns0:v>0.5216809355008342</ns0:v>
+        <ns0:v>7.250497076891118</ns0:v>
       </ns0:c>
       <ns0:c r="L47">
-        <ns0:v>68.44143978249735</ns0:v>
+        <ns0:v>68.89239374372428</ns0:v>
       </ns0:c>
       <ns0:c r="M47">
-        <ns0:v>191.06925048828126</ns0:v>
+        <ns0:v>3.60900000333786</ns0:v>
       </ns0:c>
       <ns0:c r="N47">
-        <ns0:v>164.75350006103517</ns0:v>
+        <ns0:v>3.607400002479553</ns0:v>
       </ns0:c>
       <ns0:c r="O47">
-        <ns0:v>112.13592525482177</ns0:v>
+        <ns0:v>2.4748500031232834</ns0:v>
       </ns0:c>
       <ns0:c r="P47" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q47" t="inlineStr">
@@ -3738,7 +3741,7 @@
       </ns0:c>
       <ns0:c r="T47" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/OKTA/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/NNBR/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3750,55 +3753,52 @@
       </ns0:c>
       <ns0:c r="B48" t="inlineStr">
         <ns0:is>
-          <ns0:t>P</ns0:t>
+          <ns0:t>NPAC</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C48" t="inlineStr">
         <ns0:is>
-          <ns0:t>Everpure Inc</ns0:t>
+          <ns0:t>New Providence Acquisition Corp III</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D48" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E48" t="inlineStr">
         <ns0:is>
-          <ns0:t>Computer Hardware</ns0:t>
+          <ns0:t>Shell Companies</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F48" t="inlineStr">
         <ns0:is>
-          <ns0:t>데이터 저장·관리 기술과 제품, 서비스를 제공하며 데이터 축소·보호·암호화 소프트웨어를 공급한다.</ns0:t>
+          <ns0:t>주요 영업활동 없이 기업 합병, 주식 교환, 자산 인수 등 기업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G48">
-        <ns0:v>140.13999938964844</ns0:v>
+        <ns0:v>10.539999961853027</ns0:v>
       </ns0:c>
       <ns0:c r="H48">
-        <ns0:v>4.480723393760244</ns0:v>
+        <ns0:v>0.09496893765841286</ns0:v>
       </ns0:c>
       <ns0:c r="I48">
-        <ns0:v>135.67999267578125</ns0:v>
+        <ns0:v>10.529999732971191</ns0:v>
       </ns0:c>
       <ns0:c r="J48">
-        <ns0:v>3.287151352170792</ns0:v>
-      </ns0:c>
-      <ns0:c r="K48">
-        <ns0:v>0.639702483705141</ns0:v>
+        <ns0:v>0.09496893765841286</ns0:v>
       </ns0:c>
       <ns0:c r="L48">
-        <ns0:v>78.16661281757277</ns0:v>
+        <ns0:v>75.95293098823926</ns0:v>
       </ns0:c>
       <ns0:c r="M48">
-        <ns0:v>111.65299987792969</ns0:v>
+        <ns0:v>10.48984990119934</ns0:v>
       </ns0:c>
       <ns0:c r="N48">
-        <ns0:v>102.04719985961914</ns0:v>
+        <ns0:v>10.463039932250977</ns0:v>
       </ns0:c>
       <ns0:c r="O48">
-        <ns0:v>78.61309995651246</ns0:v>
+        <ns0:v>10.356289982795715</ns0:v>
       </ns0:c>
       <ns0:c r="P48" t="inlineStr">
         <ns0:is>
@@ -3817,7 +3817,7 @@
       </ns0:c>
       <ns0:c r="T48" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/P/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/NPAC/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3829,12 +3829,12 @@
       </ns0:c>
       <ns0:c r="B49" t="inlineStr">
         <ns0:is>
-          <ns0:t>PANW</ns0:t>
+          <ns0:t>NTAP</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C49" t="inlineStr">
         <ns0:is>
-          <ns0:t>Palo Alto Networks Inc</ns0:t>
+          <ns0:t>Netapp Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D49" t="inlineStr">
@@ -3849,39 +3849,39 @@
       </ns0:c>
       <ns0:c r="F49" t="inlineStr">
         <ns0:is>
-          <ns0:t>보안 접속 서비스와 네트워크 보안 관리 등 사이버보안 솔루션을 전 세계에 제공하는 기업.</ns0:t>
+          <ns0:t>기업의 데이터 인프라 전환을 위한 소프트웨어, 시스템 및 서비스를 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G49">
-        <ns0:v>403.239990234375</ns0:v>
+        <ns0:v>226.27000427246094</ns0:v>
       </ns0:c>
       <ns0:c r="H49">
-        <ns0:v>1.7640353903785488</ns0:v>
+        <ns0:v>5.2173917979451145</ns0:v>
       </ns0:c>
       <ns0:c r="I49">
-        <ns0:v>404.69000244140625</ns0:v>
+        <ns0:v>216.80999755859375</ns0:v>
       </ns0:c>
       <ns0:c r="J49">
-        <ns0:v>-0.3583019591004599</ns0:v>
+        <ns0:v>4.3632705227583335</ns0:v>
       </ns0:c>
       <ns0:c r="K49">
-        <ns0:v>0.7582253510291649</ns0:v>
+        <ns0:v>1.9725196907150218</ns0:v>
       </ns0:c>
       <ns0:c r="L49">
-        <ns0:v>62.60249596625166</ns0:v>
+        <ns0:v>75.92517280506357</ns0:v>
       </ns0:c>
       <ns0:c r="M49">
-        <ns0:v>370.969499206543</ns0:v>
+        <ns0:v>197.87600021362306</ns0:v>
       </ns0:c>
       <ns0:c r="N49">
-        <ns0:v>361.86079956054687</ns0:v>
+        <ns0:v>192.3292007446289</ns0:v>
       </ns0:c>
       <ns0:c r="O49">
-        <ns0:v>250.34009986877442</ns0:v>
+        <ns0:v>138.75979988098143</ns0:v>
       </ns0:c>
       <ns0:c r="P49" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q49" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </ns0:c>
       <ns0:c r="T49" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/PANW/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/NTAP/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3908,59 +3908,59 @@
       </ns0:c>
       <ns0:c r="B50" t="inlineStr">
         <ns0:is>
-          <ns0:t>PBF</ns0:t>
+          <ns0:t>NTWK</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C50" t="inlineStr">
         <ns0:is>
-          <ns0:t>PBF Energy Inc</ns0:t>
+          <ns0:t>Netsol Technologies Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D50" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E50" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas Refining &amp; Marketing</ns0:t>
+          <ns0:t>Software - Application</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F50" t="inlineStr">
         <ns0:is>
-          <ns0:t>정유·물류 사업을 통해 휘발유·경유·항공유·윤활유·석유화학제품·아스팔트 등을 생산·공급하는 기업.</ns0:t>
+          <ns0:t>자동차 금융·리스, 은행 및 금융서비스 산업용 기업 소프트웨어를 설계·개발·판매하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G50">
-        <ns0:v>80.77999877929688</ns0:v>
+        <ns0:v>5.949999809265137</ns0:v>
       </ns0:c>
       <ns0:c r="H50">
-        <ns0:v>-1.8945805537713856</ns0:v>
+        <ns0:v>3.4782575524371584</ns0:v>
       </ns0:c>
       <ns0:c r="I50">
-        <ns0:v>82.61000061035156</ns0:v>
+        <ns0:v>5.869999885559082</ns0:v>
       </ns0:c>
       <ns0:c r="J50">
-        <ns0:v>-2.2152303807456697</ns0:v>
+        <ns0:v>1.3628607370651524</ns0:v>
       </ns0:c>
       <ns0:c r="K50">
-        <ns0:v>0.998164562323084</ns0:v>
+        <ns0:v>1.519630724547482</ns0:v>
       </ns0:c>
       <ns0:c r="L50">
-        <ns0:v>62.13732246287252</ns0:v>
+        <ns0:v>85.15649476886331</ns0:v>
       </ns0:c>
       <ns0:c r="M50">
-        <ns0:v>75.40400085449218</ns0:v>
+        <ns0:v>4.637499976158142</ns0:v>
       </ns0:c>
       <ns0:c r="N50">
-        <ns0:v>71.67980018615722</ns0:v>
+        <ns0:v>4.358200025558472</ns0:v>
       </ns0:c>
       <ns0:c r="O50">
-        <ns0:v>48.25095004081726</ns0:v>
+        <ns0:v>3.882200005054474</ns0:v>
       </ns0:c>
       <ns0:c r="P50" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q50" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </ns0:c>
       <ns0:c r="T50" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/PBF/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/NTWK/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -3987,55 +3987,55 @@
       </ns0:c>
       <ns0:c r="B51" t="inlineStr">
         <ns0:is>
-          <ns0:t>PRLB</ns0:t>
+          <ns0:t>NVDA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C51" t="inlineStr">
         <ns0:is>
-          <ns0:t>Proto Labs Inc</ns0:t>
+          <ns0:t>NVIDIA Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D51" t="inlineStr">
         <ns0:is>
-          <ns0:t>Industrials</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E51" t="inlineStr">
         <ns0:is>
-          <ns0:t>Metal Fabrication</ns0:t>
+          <ns0:t>Semiconductors</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F51" t="inlineStr">
         <ns0:is>
-          <ns0:t>맞춤형 부품의 디지털 제조업체로 성형, CNC 가공, 3D 프린팅, 판금 제조 서비스를 제공한다.</ns0:t>
+          <ns0:t>컴퓨팅·네트워킹 및 그래픽 부문을 운영하는 데이터센터 규모의 AI 인프라 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G51">
-        <ns0:v>98.20999908447266</ns0:v>
+        <ns0:v>233.9499969482422</ns0:v>
       </ns0:c>
       <ns0:c r="H51">
-        <ns0:v>4.069085754084822</ns0:v>
+        <ns0:v>1.3384719439145876</ns0:v>
       </ns0:c>
       <ns0:c r="I51">
-        <ns0:v>98.5</ns0:v>
+        <ns0:v>236.5399932861328</ns0:v>
       </ns0:c>
       <ns0:c r="J51">
-        <ns0:v>-0.29441717312420623</ns0:v>
+        <ns0:v>-1.0949507108329093</ns0:v>
       </ns0:c>
       <ns0:c r="K51">
-        <ns0:v>0.9212292947181998</ns0:v>
+        <ns0:v>1.2271473653136626</ns0:v>
       </ns0:c>
       <ns0:c r="L51">
-        <ns0:v>72.0772283833367</ns0:v>
+        <ns0:v>62.897434590233345</ns0:v>
       </ns0:c>
       <ns0:c r="M51">
-        <ns0:v>87.75449981689454</ns0:v>
+        <ns0:v>223.78600006103517</ns0:v>
       </ns0:c>
       <ns0:c r="N51">
-        <ns0:v>84.4845997619629</ns0:v>
+        <ns0:v>218.27820007324217</ns0:v>
       </ns0:c>
       <ns0:c r="O51">
-        <ns0:v>69.65155002593994</ns0:v>
+        <ns0:v>200.71460006713866</ns0:v>
       </ns0:c>
       <ns0:c r="P51" t="inlineStr">
         <ns0:is>
@@ -4054,7 +4054,7 @@
       </ns0:c>
       <ns0:c r="T51" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/PRLB/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/NVDA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4066,12 +4066,12 @@
       </ns0:c>
       <ns0:c r="B52" t="inlineStr">
         <ns0:is>
-          <ns0:t>PUBM</ns0:t>
+          <ns0:t>OKTA</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C52" t="inlineStr">
         <ns0:is>
-          <ns0:t>PubMatic Inc</ns0:t>
+          <ns0:t>Okta Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D52" t="inlineStr">
@@ -4081,40 +4081,40 @@
       </ns0:c>
       <ns0:c r="E52" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Application</ns0:t>
+          <ns0:t>Software - Infrastructure</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F52" t="inlineStr">
         <ns0:is>
-          <ns0:t>콘텐츠 제작자와 광고주 등에 실시간 자동화 광고 거래용 클라우드 인프라 플랫폼을 제공하는 회사.</ns0:t>
+          <ns0:t>미국과 해외에서 싱글 사인온과 위험 기반 다중요소 인증 등 신원·접근 보안 서비스를 제공하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G52">
-        <ns0:v>18.420000076293945</ns0:v>
+        <ns0:v>211.49000549316406</ns0:v>
       </ns0:c>
       <ns0:c r="H52">
-        <ns0:v>-3.962462027056113</ns0:v>
+        <ns0:v>-0.5361422957577133</ns0:v>
       </ns0:c>
       <ns0:c r="I52">
-        <ns0:v>19.299999237060547</ns0:v>
+        <ns0:v>213.86000061035156</ns0:v>
       </ns0:c>
       <ns0:c r="J52">
-        <ns0:v>-4.559581324111117</ns0:v>
+        <ns0:v>-1.1081993408882385</ns0:v>
       </ns0:c>
       <ns0:c r="K52">
-        <ns0:v>1.2113797594635038</ns0:v>
+        <ns0:v>0.5219757700945917</ns0:v>
       </ns0:c>
       <ns0:c r="L52">
-        <ns0:v>60.64021201175941</ns0:v>
+        <ns0:v>68.44143978249735</ns0:v>
       </ns0:c>
       <ns0:c r="M52">
-        <ns0:v>17.529249954223634</ns0:v>
+        <ns0:v>191.06925048828126</ns0:v>
       </ns0:c>
       <ns0:c r="N52">
-        <ns0:v>16.399500007629396</ns0:v>
+        <ns0:v>164.75350006103517</ns0:v>
       </ns0:c>
       <ns0:c r="O52">
-        <ns0:v>11.221225006580353</ns0:v>
+        <ns0:v>112.13592525482177</ns0:v>
       </ns0:c>
       <ns0:c r="P52" t="inlineStr">
         <ns0:is>
@@ -4133,7 +4133,7 @@
       </ns0:c>
       <ns0:c r="T52" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/PUBM/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/OKTA/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4145,12 +4145,12 @@
       </ns0:c>
       <ns0:c r="B53" t="inlineStr">
         <ns0:is>
-          <ns0:t>QMCO</ns0:t>
+          <ns0:t>P</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C53" t="inlineStr">
         <ns0:is>
-          <ns0:t>Quantum Corp</ns0:t>
+          <ns0:t>Everpure Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D53" t="inlineStr">
@@ -4165,39 +4165,39 @@
       </ns0:c>
       <ns0:c r="F53" t="inlineStr">
         <ns0:is>
-          <ns0:t>비정형 데이터 관리 솔루션과 영상 편집·후반 제작 등에 쓰이는 저장 소프트웨어 및 시스템을 제공한다.</ns0:t>
+          <ns0:t>데이터 저장·관리 기술과 제품, 서비스를 제공하며 데이터 축소·보호·암호화 소프트웨어를 공급한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G53">
-        <ns0:v>34.5</ns0:v>
+        <ns0:v>140.13999938964844</ns0:v>
       </ns0:c>
       <ns0:c r="H53">
-        <ns0:v>8.184385889950118</ns0:v>
+        <ns0:v>4.480723393760244</ns0:v>
       </ns0:c>
       <ns0:c r="I53">
-        <ns0:v>34.68000030517578</ns0:v>
+        <ns0:v>135.67999267578125</ns0:v>
       </ns0:c>
       <ns0:c r="J53">
-        <ns0:v>-0.5190320172774543</ns0:v>
+        <ns0:v>3.287151352170792</ns0:v>
       </ns0:c>
       <ns0:c r="K53">
-        <ns0:v>2.1048698535539594</ns0:v>
+        <ns0:v>0.642174163605049</ns0:v>
       </ns0:c>
       <ns0:c r="L53">
-        <ns0:v>77.25052225065733</ns0:v>
+        <ns0:v>78.16661281757277</ns0:v>
       </ns0:c>
       <ns0:c r="M53">
-        <ns0:v>27.062499904632567</ns0:v>
+        <ns0:v>111.65299987792969</ns0:v>
       </ns0:c>
       <ns0:c r="N53">
-        <ns0:v>21.793599967956542</ns0:v>
+        <ns0:v>102.04719985961914</ns0:v>
       </ns0:c>
       <ns0:c r="O53">
-        <ns0:v>11.500199990272522</ns0:v>
+        <ns0:v>78.61309995651246</ns0:v>
       </ns0:c>
       <ns0:c r="P53" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q53" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </ns0:c>
       <ns0:c r="T53" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/QMCO/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/P/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4224,59 +4224,56 @@
       </ns0:c>
       <ns0:c r="B54" t="inlineStr">
         <ns0:is>
-          <ns0:t>RBRK</ns0:t>
+          <ns0:t>PAII</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C54" t="inlineStr">
         <ns0:is>
-          <ns0:t>Rubrik Inc</ns0:t>
+          <ns0:t>Pyrophyte Acquisition Corp II</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D54" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E54" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Infrastructure</ns0:t>
+          <ns0:t>Shell Companies</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F54" t="inlineStr">
         <ns0:is>
-          <ns0:t>기업·클라우드·SaaS 데이터 보호, 데이터 위협 분석 및 신원 복구 등 보안 솔루션을 제공하는 회사.</ns0:t>
+          <ns0:t>현재 주요 영업 활동은 없으며 에너지 분야 기업과의 합병·인수 등 사업 결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G54">
-        <ns0:v>118.58000183105469</ns0:v>
+        <ns0:v>10.329999923706055</ns0:v>
       </ns0:c>
       <ns0:c r="H54">
-        <ns0:v>2.7556328103363725</ns0:v>
+        <ns0:v>0.0</ns0:v>
       </ns0:c>
       <ns0:c r="I54">
-        <ns0:v>117.05000305175781</ns0:v>
+        <ns0:v>10.329999923706055</ns0:v>
       </ns0:c>
       <ns0:c r="J54">
-        <ns0:v>1.3071326265752692</ns0:v>
-      </ns0:c>
-      <ns0:c r="K54">
-        <ns0:v>0.992678759433242</ns0:v>
+        <ns0:v>0.0</ns0:v>
       </ns0:c>
       <ns0:c r="L54">
-        <ns0:v>67.44245722391886</ns0:v>
+        <ns0:v>87.24938821373995</ns0:v>
       </ns0:c>
       <ns0:c r="M54">
-        <ns0:v>105.65050048828125</ns0:v>
+        <ns0:v>10.304250049591065</ns0:v>
       </ns0:c>
       <ns0:c r="N54">
-        <ns0:v>96.18160003662109</ns0:v>
+        <ns0:v>10.2775</ns0:v>
       </ns0:c>
       <ns0:c r="O54">
-        <ns0:v>71.85745002746582</ns0:v>
+        <ns0:v>10.182554941177369</ns0:v>
       </ns0:c>
       <ns0:c r="P54" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q54" t="inlineStr">
@@ -4291,7 +4288,7 @@
       </ns0:c>
       <ns0:c r="T54" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/RBRK/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/PAII/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4303,59 +4300,59 @@
       </ns0:c>
       <ns0:c r="B55" t="inlineStr">
         <ns0:is>
-          <ns0:t>RCEL</ns0:t>
+          <ns0:t>PANW</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C55" t="inlineStr">
         <ns0:is>
-          <ns0:t>AVITA Medical Inc</ns0:t>
+          <ns0:t>Palo Alto Networks Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D55" t="inlineStr">
         <ns0:is>
-          <ns0:t>Healthcare</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E55" t="inlineStr">
         <ns0:is>
-          <ns0:t>Medical Devices</ns0:t>
+          <ns0:t>Software - Infrastructure</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F55" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·일본·유럽 등에서 급성 상처 치료 사업을 하며, 주력 제품은 세포 채취 장치 RECELL 시스템.</ns0:t>
+          <ns0:t>보안 접속 서비스와 네트워크 보안 관리 등 사이버보안 솔루션을 전 세계에 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G55">
-        <ns0:v>12.720000267028809</ns0:v>
+        <ns0:v>403.239990234375</ns0:v>
       </ns0:c>
       <ns0:c r="H55">
-        <ns0:v>5.911740421449396</ns0:v>
+        <ns0:v>1.7640353903785488</ns0:v>
       </ns0:c>
       <ns0:c r="I55">
-        <ns0:v>12.399999618530273</ns0:v>
+        <ns0:v>404.69000244140625</ns0:v>
       </ns0:c>
       <ns0:c r="J55">
-        <ns0:v>2.5806504705075506</ns0:v>
+        <ns0:v>-0.3583019591004599</ns0:v>
       </ns0:c>
       <ns0:c r="K55">
-        <ns0:v>1.2954199231686316</ns0:v>
+        <ns0:v>0.7700308580678029</ns0:v>
       </ns0:c>
       <ns0:c r="L55">
-        <ns0:v>71.24372251472865</ns0:v>
+        <ns0:v>62.60249596625166</ns0:v>
       </ns0:c>
       <ns0:c r="M55">
-        <ns0:v>11.069499969482422</ns0:v>
+        <ns0:v>370.969499206543</ns0:v>
       </ns0:c>
       <ns0:c r="N55">
-        <ns0:v>9.129800004959106</ns0:v>
+        <ns0:v>361.86079956054687</ns0:v>
       </ns0:c>
       <ns0:c r="O55">
-        <ns0:v>5.466150010824204</ns0:v>
+        <ns0:v>250.34009986877442</ns0:v>
       </ns0:c>
       <ns0:c r="P55" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q55" t="inlineStr">
@@ -4370,7 +4367,7 @@
       </ns0:c>
       <ns0:c r="T55" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/RCEL/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/PANW/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4382,59 +4379,59 @@
       </ns0:c>
       <ns0:c r="B56" t="inlineStr">
         <ns0:is>
-          <ns0:t>S</ns0:t>
+          <ns0:t>PBF</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C56" t="inlineStr">
         <ns0:is>
-          <ns0:t>SentinelOne Inc</ns0:t>
+          <ns0:t>PBF Energy Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D56" t="inlineStr">
         <ns0:is>
-          <ns0:t>Technology</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E56" t="inlineStr">
         <ns0:is>
-          <ns0:t>Software - Infrastructure</ns0:t>
+          <ns0:t>Oil &amp; Gas Refining &amp; Marketing</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F56" t="inlineStr">
         <ns0:is>
-          <ns0:t>AI 기반 Singularity 플랫폼으로 단말·클라우드·신원 인증정보의 위협 예방·탐지·대응을 제공하는 회사.</ns0:t>
+          <ns0:t>정유·물류 사업을 통해 휘발유·경유·항공유·윤활유·석유화학제품·아스팔트 등을 생산·공급하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G56">
-        <ns0:v>25.059999465942383</ns0:v>
+        <ns0:v>80.77999877929688</ns0:v>
       </ns0:c>
       <ns0:c r="H56">
-        <ns0:v>1.5808649713916934</ns0:v>
+        <ns0:v>-1.8945805537713856</ns0:v>
       </ns0:c>
       <ns0:c r="I56">
-        <ns0:v>24.690000534057617</ns0:v>
+        <ns0:v>82.61000061035156</ns0:v>
       </ns0:c>
       <ns0:c r="J56">
-        <ns0:v>1.4985780635135448</ns0:v>
+        <ns0:v>-2.2152303807456697</ns0:v>
       </ns0:c>
       <ns0:c r="K56">
-        <ns0:v>1.2644349655155076</ns0:v>
+        <ns0:v>1.001159316951186</ns0:v>
       </ns0:c>
       <ns0:c r="L56">
-        <ns0:v>65.39309224280834</ns0:v>
+        <ns0:v>62.13732246287252</ns0:v>
       </ns0:c>
       <ns0:c r="M56">
-        <ns0:v>22.545999908447264</ns0:v>
+        <ns0:v>75.40400085449218</ns0:v>
       </ns0:c>
       <ns0:c r="N56">
-        <ns0:v>21.510199851989746</ns0:v>
+        <ns0:v>71.67980018615722</ns0:v>
       </ns0:c>
       <ns0:c r="O56">
-        <ns0:v>16.68499993801117</ns0:v>
+        <ns0:v>48.25095004081726</ns0:v>
       </ns0:c>
       <ns0:c r="P56" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q56" t="inlineStr">
@@ -4449,7 +4446,7 @@
       </ns0:c>
       <ns0:c r="T56" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/S/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/PBF/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4461,59 +4458,59 @@
       </ns0:c>
       <ns0:c r="B57" t="inlineStr">
         <ns0:is>
-          <ns0:t>SAFT</ns0:t>
+          <ns0:t>PRLB</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C57" t="inlineStr">
         <ns0:is>
-          <ns0:t>Safety Insurance Group Inc</ns0:t>
+          <ns0:t>Proto Labs Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D57" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Industrials</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E57" t="inlineStr">
         <ns0:is>
-          <ns0:t>Insurance - Property &amp; Casualty</ns0:t>
+          <ns0:t>Metal Fabrication</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F57" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 매사추세츠주에서 개인용·상업용 자동차보험과 주택 소유자 보험을 제공하는 회사.</ns0:t>
+          <ns0:t>맞춤형 부품의 디지털 제조업체로 성형, CNC 가공, 3D 프린팅, 판금 제조 서비스를 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G57">
-        <ns0:v>103.91999816894531</ns0:v>
+        <ns0:v>98.20999908447266</ns0:v>
       </ns0:c>
       <ns0:c r="H57">
-        <ns0:v>0.1059634071270299</ns0:v>
+        <ns0:v>4.069085754084822</ns0:v>
       </ns0:c>
       <ns0:c r="I57">
-        <ns0:v>103.9000015258789</ns0:v>
+        <ns0:v>98.5</ns0:v>
       </ns0:c>
       <ns0:c r="J57">
-        <ns0:v>0.019246046941989725</ns0:v>
+        <ns0:v>-0.29441717312420623</ns0:v>
       </ns0:c>
       <ns0:c r="K57">
-        <ns0:v>0.9800596874263724</ns0:v>
+        <ns0:v>1.004687988332118</ns0:v>
       </ns0:c>
       <ns0:c r="L57">
-        <ns0:v>75.29368421069051</ns0:v>
+        <ns0:v>72.0772283833367</ns0:v>
       </ns0:c>
       <ns0:c r="M57">
-        <ns0:v>103.51850051879883</ns0:v>
+        <ns0:v>87.75449981689454</ns0:v>
       </ns0:c>
       <ns0:c r="N57">
-        <ns0:v>103.44800018310546</ns0:v>
+        <ns0:v>84.4845997619629</ns0:v>
       </ns0:c>
       <ns0:c r="O57">
-        <ns0:v>82.02189994812012</ns0:v>
+        <ns0:v>69.65155002593994</ns0:v>
       </ns0:c>
       <ns0:c r="P57" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q57" t="inlineStr">
@@ -4528,7 +4525,7 @@
       </ns0:c>
       <ns0:c r="T57" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/SAFT/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/PRLB/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4540,12 +4537,12 @@
       </ns0:c>
       <ns0:c r="B58" t="inlineStr">
         <ns0:is>
-          <ns0:t>SILC</ns0:t>
+          <ns0:t>PUBM</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C58" t="inlineStr">
         <ns0:is>
-          <ns0:t>Silicom Ltd</ns0:t>
+          <ns0:t>PubMatic Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D58" t="inlineStr">
@@ -4555,44 +4552,44 @@
       </ns0:c>
       <ns0:c r="E58" t="inlineStr">
         <ns0:is>
-          <ns0:t>Communication Equipment</ns0:t>
+          <ns0:t>Software - Application</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F58" t="inlineStr">
         <ns0:is>
-          <ns0:t>서버 네트워크 인터페이스 카드와 암호화·압축용 카드 등 네트워크·데이터 인프라 솔루션을 설계·제조·판매.</ns0:t>
+          <ns0:t>콘텐츠 제작자와 광고주 등에 실시간 자동화 광고 거래용 클라우드 인프라 플랫폼을 제공하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G58">
-        <ns0:v>60.029998779296875</ns0:v>
+        <ns0:v>18.420000076293945</ns0:v>
       </ns0:c>
       <ns0:c r="H58">
-        <ns0:v>11.93361473749186</ns0:v>
+        <ns0:v>-3.962462027056113</ns0:v>
       </ns0:c>
       <ns0:c r="I58">
-        <ns0:v>54.25</ns0:v>
+        <ns0:v>19.299999237060547</ns0:v>
       </ns0:c>
       <ns0:c r="J58">
-        <ns0:v>10.654375630040324</ns0:v>
+        <ns0:v>-4.559581324111117</ns0:v>
       </ns0:c>
       <ns0:c r="K58">
-        <ns0:v>1.7924519079705339</ns0:v>
+        <ns0:v>1.2114116277780858</ns0:v>
       </ns0:c>
       <ns0:c r="L58">
-        <ns0:v>74.21247254564288</ns0:v>
+        <ns0:v>60.64021201175941</ns0:v>
       </ns0:c>
       <ns0:c r="M58">
-        <ns0:v>47.36949996948242</ns0:v>
+        <ns0:v>17.529249954223634</ns0:v>
       </ns0:c>
       <ns0:c r="N58">
-        <ns0:v>44.54940002441406</ns0:v>
+        <ns0:v>16.399500007629396</ns0:v>
       </ns0:c>
       <ns0:c r="O58">
-        <ns0:v>32.77899994373322</ns0:v>
+        <ns0:v>11.221225006580353</ns0:v>
       </ns0:c>
       <ns0:c r="P58" t="inlineStr">
         <ns0:is>
-          <ns0:t>종가 돌파</ns0:t>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q58" t="inlineStr">
@@ -4607,7 +4604,7 @@
       </ns0:c>
       <ns0:c r="T58" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/SILC/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/PUBM/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4619,12 +4616,12 @@
       </ns0:c>
       <ns0:c r="B59" t="inlineStr">
         <ns0:is>
-          <ns0:t>SLAB</ns0:t>
+          <ns0:t>QMCO</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C59" t="inlineStr">
         <ns0:is>
-          <ns0:t>Silicon Laboratories Inc</ns0:t>
+          <ns0:t>Quantum Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D59" t="inlineStr">
@@ -4634,40 +4631,40 @@
       </ns0:c>
       <ns0:c r="E59" t="inlineStr">
         <ns0:is>
-          <ns0:t>Semiconductors</ns0:t>
+          <ns0:t>Computer Hardware</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F59" t="inlineStr">
         <ns0:is>
-          <ns0:t>산업용 사물인터넷 등 전자제품에 쓰이는 아날로그 중심 혼합신호 제품을 공급하는 팹리스 반도체 기업.</ns0:t>
+          <ns0:t>비정형 데이터 관리 솔루션과 영상 편집·후반 제작 등에 쓰이는 저장 소프트웨어 및 시스템을 제공한다.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G59">
-        <ns0:v>222.75999450683594</ns0:v>
+        <ns0:v>34.5</ns0:v>
       </ns0:c>
       <ns0:c r="H59">
-        <ns0:v>0.11235450369502242</ns0:v>
+        <ns0:v>8.184385889950118</ns0:v>
       </ns0:c>
       <ns0:c r="I59">
-        <ns0:v>222.9199981689453</ns0:v>
+        <ns0:v>34.68000030517578</ns0:v>
       </ns0:c>
       <ns0:c r="J59">
-        <ns0:v>-0.07177627104953954</ns0:v>
+        <ns0:v>-0.5190320172774543</ns0:v>
       </ns0:c>
       <ns0:c r="K59">
-        <ns0:v>0.8727567091948966</ns0:v>
+        <ns0:v>2.106431787595817</ns0:v>
       </ns0:c>
       <ns0:c r="L59">
-        <ns0:v>68.46217124488129</ns0:v>
+        <ns0:v>77.25052225065733</ns0:v>
       </ns0:c>
       <ns0:c r="M59">
-        <ns0:v>220.7400001525879</ns0:v>
+        <ns0:v>27.062499904632567</ns0:v>
       </ns0:c>
       <ns0:c r="N59">
-        <ns0:v>219.3497998046875</ns0:v>
+        <ns0:v>21.793599967956542</ns0:v>
       </ns0:c>
       <ns0:c r="O59">
-        <ns0:v>202.60630020141602</ns0:v>
+        <ns0:v>11.500199990272522</ns0:v>
       </ns0:c>
       <ns0:c r="P59" t="inlineStr">
         <ns0:is>
@@ -4686,7 +4683,7 @@
       </ns0:c>
       <ns0:c r="T59" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/SLAB/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/QMCO/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4698,12 +4695,12 @@
       </ns0:c>
       <ns0:c r="B60" t="inlineStr">
         <ns0:is>
-          <ns0:t>SMTC</ns0:t>
+          <ns0:t>RBRK</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C60" t="inlineStr">
         <ns0:is>
-          <ns0:t>Semtech Corp</ns0:t>
+          <ns0:t>Rubrik Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D60" t="inlineStr">
@@ -4713,40 +4710,40 @@
       </ns0:c>
       <ns0:c r="E60" t="inlineStr">
         <ns0:is>
-          <ns0:t>Semiconductors</ns0:t>
+          <ns0:t>Software - Infrastructure</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F60" t="inlineStr">
         <ns0:is>
-          <ns0:t>반도체, 사물인터넷 시스템, 클라우드 연결 서비스를 제공하는 기업.</ns0:t>
+          <ns0:t>기업·클라우드·SaaS 데이터 보호, 데이터 위협 분석 및 신원 복구 등 보안 솔루션을 제공하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G60">
-        <ns0:v>194.8800048828125</ns0:v>
+        <ns0:v>118.58000183105469</ns0:v>
       </ns0:c>
       <ns0:c r="H60">
-        <ns0:v>4.442900856222609</ns0:v>
+        <ns0:v>2.7556328103363725</ns0:v>
       </ns0:c>
       <ns0:c r="I60">
-        <ns0:v>190.63999938964844</ns0:v>
+        <ns0:v>117.05000305175781</ns0:v>
       </ns0:c>
       <ns0:c r="J60">
-        <ns0:v>2.2240901734886798</ns0:v>
+        <ns0:v>1.3071326265752692</ns0:v>
       </ns0:c>
       <ns0:c r="K60">
-        <ns0:v>1.463727258901867</ns0:v>
+        <ns0:v>1.0035120994639428</ns0:v>
       </ns0:c>
       <ns0:c r="L60">
-        <ns0:v>66.11357828047912</ns0:v>
+        <ns0:v>67.44245722391886</ns0:v>
       </ns0:c>
       <ns0:c r="M60">
-        <ns0:v>171.1025016784668</ns0:v>
+        <ns0:v>105.65050048828125</ns0:v>
       </ns0:c>
       <ns0:c r="N60">
-        <ns0:v>145.95860076904296</ns0:v>
+        <ns0:v>96.18160003662109</ns0:v>
       </ns0:c>
       <ns0:c r="O60">
-        <ns0:v>116.8936503982544</ns0:v>
+        <ns0:v>71.85745002746582</ns0:v>
       </ns0:c>
       <ns0:c r="P60" t="inlineStr">
         <ns0:is>
@@ -4765,7 +4762,7 @@
       </ns0:c>
       <ns0:c r="T60" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/SMTC/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/RBRK/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4777,59 +4774,59 @@
       </ns0:c>
       <ns0:c r="B61" t="inlineStr">
         <ns0:is>
-          <ns0:t>TNK</ns0:t>
+          <ns0:t>RCEL</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C61" t="inlineStr">
         <ns0:is>
-          <ns0:t>Teekay Tankers Ltd</ns0:t>
+          <ns0:t>AVITA Medical Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D61" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Healthcare</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E61" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas Midstream</ns0:t>
+          <ns0:t>Medical Devices</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F61" t="inlineStr">
         <ns0:is>
-          <ns0:t>석유업계에 해상 운송, 항해·기간 용선, 해상 선박 간 화물 이송 서비스를 제공하는 기업.</ns0:t>
+          <ns0:t>미국·일본·유럽 등에서 급성 상처 치료 사업을 하며, 주력 제품은 세포 채취 장치 RECELL 시스템.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G61">
-        <ns0:v>103.0999984741211</ns0:v>
+        <ns0:v>12.720000267028809</ns0:v>
       </ns0:c>
       <ns0:c r="H61">
-        <ns0:v>2.06909839985141</ns0:v>
+        <ns0:v>5.911740421449396</ns0:v>
       </ns0:c>
       <ns0:c r="I61">
-        <ns0:v>103.16000366210938</ns0:v>
+        <ns0:v>12.399999618530273</ns0:v>
       </ns0:c>
       <ns0:c r="J61">
-        <ns0:v>-0.05816710532972058</ns0:v>
+        <ns0:v>2.5806504705075506</ns0:v>
       </ns0:c>
       <ns0:c r="K61">
-        <ns0:v>1.2935549705699665</ns0:v>
+        <ns0:v>1.2955358325606041</ns0:v>
       </ns0:c>
       <ns0:c r="L61">
-        <ns0:v>69.55785273076296</ns0:v>
+        <ns0:v>71.24372251472865</ns0:v>
       </ns0:c>
       <ns0:c r="M61">
-        <ns0:v>97.67249984741211</ns0:v>
+        <ns0:v>11.069499969482422</ns0:v>
       </ns0:c>
       <ns0:c r="N61">
-        <ns0:v>89.20059982299804</ns0:v>
+        <ns0:v>9.129800004959106</ns0:v>
       </ns0:c>
       <ns0:c r="O61">
-        <ns0:v>74.71469966888428</ns0:v>
+        <ns0:v>5.466150010824204</ns0:v>
       </ns0:c>
       <ns0:c r="P61" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q61" t="inlineStr">
@@ -4844,7 +4841,7 @@
       </ns0:c>
       <ns0:c r="T61" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/TNK/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/RCEL/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4856,55 +4853,55 @@
       </ns0:c>
       <ns0:c r="B62" t="inlineStr">
         <ns0:is>
-          <ns0:t>TRMD</ns0:t>
+          <ns0:t>S</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C62" t="inlineStr">
         <ns0:is>
-          <ns0:t>Torm Plc</ns0:t>
+          <ns0:t>SentinelOne Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D62" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E62" t="inlineStr">
         <ns0:is>
-          <ns0:t>Oil &amp; Gas Midstream</ns0:t>
+          <ns0:t>Software - Infrastructure</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F62" t="inlineStr">
         <ns0:is>
-          <ns0:t>석유제품 운반선을 보유·운영하며 휘발유·항공유 등 정제유 운송과 해양 엔지니어링 사업을 하는 회사.</ns0:t>
+          <ns0:t>AI 기반 Singularity 플랫폼으로 단말·클라우드·신원 인증정보의 위협 예방·탐지·대응을 제공하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G62">
-        <ns0:v>40.0</ns0:v>
+        <ns0:v>25.059999465942383</ns0:v>
       </ns0:c>
       <ns0:c r="H62">
-        <ns0:v>3.0927855323080733</ns0:v>
+        <ns0:v>1.5808649713916934</ns0:v>
       </ns0:c>
       <ns0:c r="I62">
-        <ns0:v>38.939998626708984</ns0:v>
+        <ns0:v>24.690000534057617</ns0:v>
       </ns0:c>
       <ns0:c r="J62">
-        <ns0:v>2.722140243127691</ns0:v>
+        <ns0:v>1.4985780635135448</ns0:v>
       </ns0:c>
       <ns0:c r="K62">
-        <ns0:v>0.9001949327086535</ns0:v>
+        <ns0:v>1.2645822334330576</ns0:v>
       </ns0:c>
       <ns0:c r="L62">
-        <ns0:v>72.48121099198185</ns0:v>
+        <ns0:v>65.39309224280834</ns0:v>
       </ns0:c>
       <ns0:c r="M62">
-        <ns0:v>36.009999656677245</ns0:v>
+        <ns0:v>22.545999908447264</ns0:v>
       </ns0:c>
       <ns0:c r="N62">
-        <ns0:v>32.802799758911135</ns0:v>
+        <ns0:v>21.510199851989746</ns0:v>
       </ns0:c>
       <ns0:c r="O62">
-        <ns0:v>28.740124950408937</ns0:v>
+        <ns0:v>16.68499993801117</ns0:v>
       </ns0:c>
       <ns0:c r="P62" t="inlineStr">
         <ns0:is>
@@ -4923,7 +4920,7 @@
       </ns0:c>
       <ns0:c r="T62" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/TRMD/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/S/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -4935,55 +4932,55 @@
       </ns0:c>
       <ns0:c r="B63" t="inlineStr">
         <ns0:is>
-          <ns0:t>TWIN</ns0:t>
+          <ns0:t>SAFT</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C63" t="inlineStr">
         <ns0:is>
-          <ns0:t>Twin Disc Incorporated</ns0:t>
+          <ns0:t>Safety Insurance Group Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D63" t="inlineStr">
         <ns0:is>
-          <ns0:t>Industrials</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E63" t="inlineStr">
         <ns0:is>
-          <ns0:t>Specialty Industrial Machinery</ns0:t>
+          <ns0:t>Insurance - Property &amp; Casualty</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F63" t="inlineStr">
         <ns0:is>
-          <ns0:t>선박 및 대형 비도로용 동력전달 장비를 설계·제조·판매하며 제조와 유통 부문을 운영한다.</ns0:t>
+          <ns0:t>미국 매사추세츠주에서 개인용·상업용 자동차보험과 주택 소유자 보험을 제공하는 회사.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G63">
-        <ns0:v>28.5049991607666</ns0:v>
+        <ns0:v>103.91999816894531</ns0:v>
       </ns0:c>
       <ns0:c r="H63">
-        <ns0:v>6.124342937583838</ns0:v>
+        <ns0:v>0.1059634071270299</ns0:v>
       </ns0:c>
       <ns0:c r="I63">
-        <ns0:v>26.959999084472656</ns0:v>
+        <ns0:v>103.9000015258789</ns0:v>
       </ns0:c>
       <ns0:c r="J63">
-        <ns0:v>5.730712643769231</ns0:v>
+        <ns0:v>0.019246046941989725</ns0:v>
       </ns0:c>
       <ns0:c r="K63">
-        <ns0:v>1.4604611345736789</ns0:v>
+        <ns0:v>0.9801303699049714</ns0:v>
       </ns0:c>
       <ns0:c r="L63">
-        <ns0:v>77.02548652039695</ns0:v>
+        <ns0:v>75.29368421069051</ns0:v>
       </ns0:c>
       <ns0:c r="M63">
-        <ns0:v>25.411250114440918</ns0:v>
+        <ns0:v>103.51850051879883</ns0:v>
       </ns0:c>
       <ns0:c r="N63">
-        <ns0:v>24.281700096130372</ns0:v>
+        <ns0:v>103.44800018310546</ns0:v>
       </ns0:c>
       <ns0:c r="O63">
-        <ns0:v>19.609425091743468</ns0:v>
+        <ns0:v>82.02189994812012</ns0:v>
       </ns0:c>
       <ns0:c r="P63" t="inlineStr">
         <ns0:is>
@@ -5002,7 +4999,7 @@
       </ns0:c>
       <ns0:c r="T63" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/TWIN/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/SAFT/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -5014,59 +5011,59 @@
       </ns0:c>
       <ns0:c r="B64" t="inlineStr">
         <ns0:is>
-          <ns0:t>VEON</ns0:t>
+          <ns0:t>SILC</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C64" t="inlineStr">
         <ns0:is>
-          <ns0:t>VEON Ltd ADR</ns0:t>
+          <ns0:t>Silicom Ltd</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D64" t="inlineStr">
         <ns0:is>
-          <ns0:t>Communication Services</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E64" t="inlineStr">
         <ns0:is>
-          <ns0:t>Telecom Services</ns0:t>
+          <ns0:t>Communication Equipment</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F64" t="inlineStr">
         <ns0:is>
-          <ns0:t>파키스탄·우크라이나·카자흐스탄·방글라데시·우즈베키스탄에서 이동통신과 디지털 서비스를 제공.</ns0:t>
+          <ns0:t>서버 네트워크 인터페이스 카드와 암호화·압축용 카드 등 네트워크·데이터 인프라 솔루션을 설계·제조·판매.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G64">
-        <ns0:v>75.63999938964844</ns0:v>
+        <ns0:v>60.029998779296875</ns0:v>
       </ns0:c>
       <ns0:c r="H64">
-        <ns0:v>2.326841535861557</ns0:v>
+        <ns0:v>11.93361473749186</ns0:v>
       </ns0:c>
       <ns0:c r="I64">
-        <ns0:v>76.02999877929688</ns0:v>
+        <ns0:v>54.25</ns0:v>
       </ns0:c>
       <ns0:c r="J64">
-        <ns0:v>-0.5129546177957245</ns0:v>
+        <ns0:v>10.654375630040324</ns0:v>
       </ns0:c>
       <ns0:c r="K64">
-        <ns0:v>0.9766252292643163</ns0:v>
+        <ns0:v>1.7952030164438082</ns0:v>
       </ns0:c>
       <ns0:c r="L64">
-        <ns0:v>71.914270872721</ns0:v>
+        <ns0:v>74.21247254564288</ns0:v>
       </ns0:c>
       <ns0:c r="M64">
-        <ns0:v>69.84600028991699</ns0:v>
+        <ns0:v>47.36949996948242</ns0:v>
       </ns0:c>
       <ns0:c r="N64">
-        <ns0:v>62.25060028076172</ns0:v>
+        <ns0:v>44.54940002441406</ns0:v>
       </ns0:c>
       <ns0:c r="O64">
-        <ns0:v>54.86120004653931</ns0:v>
+        <ns0:v>32.77899994373322</ns0:v>
       </ns0:c>
       <ns0:c r="P64" t="inlineStr">
         <ns0:is>
-          <ns0:t>장중 경신 후 밀림</ns0:t>
+          <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="Q64" t="inlineStr">
@@ -5081,7 +5078,7 @@
       </ns0:c>
       <ns0:c r="T64" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/VEON/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/SILC/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -5093,55 +5090,55 @@
       </ns0:c>
       <ns0:c r="B65" t="inlineStr">
         <ns0:is>
-          <ns0:t>VRA</ns0:t>
+          <ns0:t>SLAB</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C65" t="inlineStr">
         <ns0:is>
-          <ns0:t>Vera Bradley Inc</ns0:t>
+          <ns0:t>Silicon Laboratories Inc</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D65" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E65" t="inlineStr">
         <ns0:is>
-          <ns0:t>Footwear &amp; Accessories</ns0:t>
+          <ns0:t>Semiconductors</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F65" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국에서 여성용 핸드백, 여행 가방·용품, 패션·홈 액세서리와 선물용품을 디자인·제조한다.</ns0:t>
+          <ns0:t>산업용 사물인터넷 등 전자제품에 쓰이는 아날로그 중심 혼합신호 제품을 공급하는 팹리스 반도체 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G65">
-        <ns0:v>5.110000133514404</ns0:v>
+        <ns0:v>222.75999450683594</ns0:v>
       </ns0:c>
       <ns0:c r="H65">
-        <ns0:v>2.6104440550806185</ns0:v>
+        <ns0:v>0.11235450369502242</ns0:v>
       </ns0:c>
       <ns0:c r="I65">
-        <ns0:v>5.110000133514404</ns0:v>
+        <ns0:v>222.9199981689453</ns0:v>
       </ns0:c>
       <ns0:c r="J65">
-        <ns0:v>0.0</ns0:v>
+        <ns0:v>-0.07177627104953954</ns0:v>
       </ns0:c>
       <ns0:c r="K65">
-        <ns0:v>0.44545063294896337</ns0:v>
+        <ns0:v>1.0710074791025077</ns0:v>
       </ns0:c>
       <ns0:c r="L65">
-        <ns0:v>77.16253272002446</ns0:v>
+        <ns0:v>68.46217124488129</ns0:v>
       </ns0:c>
       <ns0:c r="M65">
-        <ns0:v>3.9680000066757204</ns0:v>
+        <ns0:v>220.7400001525879</ns0:v>
       </ns0:c>
       <ns0:c r="N65">
-        <ns0:v>3.5978000164031982</ns0:v>
+        <ns0:v>219.3497998046875</ns0:v>
       </ns0:c>
       <ns0:c r="O65">
-        <ns0:v>3.3451500058174135</ns0:v>
+        <ns0:v>202.60630020141602</ns0:v>
       </ns0:c>
       <ns0:c r="P65" t="inlineStr">
         <ns0:is>
@@ -5160,7 +5157,7 @@
       </ns0:c>
       <ns0:c r="T65" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/VRA/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/SLAB/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -5172,55 +5169,55 @@
       </ns0:c>
       <ns0:c r="B66" t="inlineStr">
         <ns0:is>
-          <ns0:t>WEYS</ns0:t>
+          <ns0:t>SMTC</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C66" t="inlineStr">
         <ns0:is>
-          <ns0:t>Weyco Group Inc</ns0:t>
+          <ns0:t>Semtech Corp</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D66" t="inlineStr">
         <ns0:is>
-          <ns0:t>Consumer Cyclical</ns0:t>
+          <ns0:t>Technology</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E66" t="inlineStr">
         <ns0:is>
-          <ns0:t>Footwear &amp; Accessories</ns0:t>
+          <ns0:t>Semiconductors</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F66" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국·캐나다·호주·아시아·남아프리카에서 남성·여성·아동용 신발을 디자인·마케팅·유통.</ns0:t>
+          <ns0:t>반도체, 사물인터넷 시스템, 클라우드 연결 서비스를 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G66">
-        <ns0:v>50.88999938964844</ns0:v>
+        <ns0:v>194.8800048828125</ns0:v>
       </ns0:c>
       <ns0:c r="H66">
-        <ns0:v>1.3543125225550234</ns0:v>
+        <ns0:v>4.442900856222609</ns0:v>
       </ns0:c>
       <ns0:c r="I66">
-        <ns0:v>50.47999954223633</ns0:v>
+        <ns0:v>190.63999938964844</ns0:v>
       </ns0:c>
       <ns0:c r="J66">
-        <ns0:v>0.8122025577061764</ns0:v>
+        <ns0:v>2.2240901734886798</ns0:v>
       </ns0:c>
       <ns0:c r="K66">
-        <ns0:v>0.8828866596795928</ns0:v>
+        <ns0:v>1.4639884777442143</ns0:v>
       </ns0:c>
       <ns0:c r="L66">
-        <ns0:v>74.85120169757123</ns0:v>
+        <ns0:v>66.11357828047912</ns0:v>
       </ns0:c>
       <ns0:c r="M66">
-        <ns0:v>46.14900016784668</ns0:v>
+        <ns0:v>171.1025016784668</ns0:v>
       </ns0:c>
       <ns0:c r="N66">
-        <ns0:v>44.68260017395019</ns0:v>
+        <ns0:v>145.95860076904296</ns0:v>
       </ns0:c>
       <ns0:c r="O66">
-        <ns0:v>36.55820008277893</ns0:v>
+        <ns0:v>116.8936503982544</ns0:v>
       </ns0:c>
       <ns0:c r="P66" t="inlineStr">
         <ns0:is>
@@ -5239,7 +5236,7 @@
       </ns0:c>
       <ns0:c r="T66" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/WEYS/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/SMTC/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -5251,55 +5248,55 @@
       </ns0:c>
       <ns0:c r="B67" t="inlineStr">
         <ns0:is>
-          <ns0:t>WTBA</ns0:t>
+          <ns0:t>TNK</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C67" t="inlineStr">
         <ns0:is>
-          <ns0:t>West Bancorporation</ns0:t>
+          <ns0:t>Teekay Tankers Ltd</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="D67" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="E67" t="inlineStr">
         <ns0:is>
-          <ns0:t>Banks - Regional</ns0:t>
+          <ns0:t>Oil &amp; Gas Midstream</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="F67" t="inlineStr">
         <ns0:is>
-          <ns0:t>미국 개인과 중소기업에 예금 등 지역 금융·신탁 서비스를 제공하는 웨스트뱅크의 은행지주회사.</ns0:t>
+          <ns0:t>석유업계에 해상 운송, 항해·기간 용선, 해상 선박 간 화물 이송 서비스를 제공하는 기업.</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="G67">
-        <ns0:v>30.079999923706055</ns0:v>
+        <ns0:v>103.0999984741211</ns0:v>
       </ns0:c>
       <ns0:c r="H67">
-        <ns0:v>4.155127416241933</ns0:v>
+        <ns0:v>2.06909839985141</ns0:v>
       </ns0:c>
       <ns0:c r="I67">
-        <ns0:v>30.329999923706055</ns0:v>
+        <ns0:v>103.16000366210938</ns0:v>
       </ns0:c>
       <ns0:c r="J67">
-        <ns0:v>-0.8242664049748272</ns0:v>
+        <ns0:v>-0.05816710532972058</ns0:v>
       </ns0:c>
       <ns0:c r="K67">
-        <ns0:v>2.459900652576215</ns0:v>
+        <ns0:v>1.308527315211926</ns0:v>
       </ns0:c>
       <ns0:c r="L67">
-        <ns0:v>62.98668498653244</ns0:v>
+        <ns0:v>69.55785273076296</ns0:v>
       </ns0:c>
       <ns0:c r="M67">
-        <ns0:v>29.167000007629394</ns0:v>
+        <ns0:v>97.67249984741211</ns0:v>
       </ns0:c>
       <ns0:c r="N67">
-        <ns0:v>28.782399978637695</ns0:v>
+        <ns0:v>89.20059982299804</ns0:v>
       </ns0:c>
       <ns0:c r="O67">
-        <ns0:v>25.433200006484984</ns0:v>
+        <ns0:v>74.71469966888428</ns0:v>
       </ns0:c>
       <ns0:c r="P67" t="inlineStr">
         <ns0:is>
@@ -5318,7 +5315,7 @@
       </ns0:c>
       <ns0:c r="T67" t="inlineStr">
         <ns0:is>
-          <ns0:t>https://finance.yahoo.com/quote/WTBA/profile/</ns0:t>
+          <ns0:t>https://finance.yahoo.com/quote/TNK/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -5330,79 +5327,553 @@
       </ns0:c>
       <ns0:c r="B68" t="inlineStr">
         <ns0:is>
+          <ns0:t>TRMD</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Torm Plc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Energy</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Oil &amp; Gas Midstream</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>석유제품 운반선을 보유·운영하며 휘발유·항공유 등 정제유 운송과 해양 엔지니어링 사업을 하는 회사.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G68">
+        <ns0:v>40.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="H68">
+        <ns0:v>3.0927855323080733</ns0:v>
+      </ns0:c>
+      <ns0:c r="I68">
+        <ns0:v>38.939998626708984</ns0:v>
+      </ns0:c>
+      <ns0:c r="J68">
+        <ns0:v>2.722140243127691</ns0:v>
+      </ns0:c>
+      <ns0:c r="K68">
+        <ns0:v>0.901917437725833</ns0:v>
+      </ns0:c>
+      <ns0:c r="L68">
+        <ns0:v>72.48121099198185</ns0:v>
+      </ns0:c>
+      <ns0:c r="M68">
+        <ns0:v>36.009999656677245</ns0:v>
+      </ns0:c>
+      <ns0:c r="N68">
+        <ns0:v>32.802799758911135</ns0:v>
+      </ns0:c>
+      <ns0:c r="O68">
+        <ns0:v>28.740124950408937</ns0:v>
+      </ns0:c>
+      <ns0:c r="P68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>재료 수집 실패</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R68" t="inlineStr">
+        <ns0:is>
+          <ns0:t/>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/TRMD/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="69">
+      <ns0:c r="A69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-10-02</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>TWIN</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Twin Disc Incorporated</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Industrials</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Specialty Industrial Machinery</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>선박 및 대형 비도로용 동력전달 장비를 설계·제조·판매하며 제조와 유통 부문을 운영한다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G69">
+        <ns0:v>28.510000228881836</ns0:v>
+      </ns0:c>
+      <ns0:c r="H69">
+        <ns0:v>6.142961954715598</ns0:v>
+      </ns0:c>
+      <ns0:c r="I69">
+        <ns0:v>26.959999084472656</ns0:v>
+      </ns0:c>
+      <ns0:c r="J69">
+        <ns0:v>5.749262600316207</ns0:v>
+      </ns0:c>
+      <ns0:c r="K69">
+        <ns0:v>1.461020431457596</ns0:v>
+      </ns0:c>
+      <ns0:c r="L69">
+        <ns0:v>77.04331219481406</ns0:v>
+      </ns0:c>
+      <ns0:c r="M69">
+        <ns0:v>25.41150016784668</ns0:v>
+      </ns0:c>
+      <ns0:c r="N69">
+        <ns0:v>24.281800117492676</ns0:v>
+      </ns0:c>
+      <ns0:c r="O69">
+        <ns0:v>19.609450097084046</ns0:v>
+      </ns0:c>
+      <ns0:c r="P69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>재료 수집 실패</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R69" t="inlineStr">
+        <ns0:is>
+          <ns0:t/>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T69" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/TWIN/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="70">
+      <ns0:c r="A70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-10-02</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>VEON</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>VEON Ltd ADR</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Communication Services</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Telecom Services</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>파키스탄·우크라이나·카자흐스탄·방글라데시·우즈베키스탄에서 이동통신과 디지털 서비스를 제공.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G70">
+        <ns0:v>75.63999938964844</ns0:v>
+      </ns0:c>
+      <ns0:c r="H70">
+        <ns0:v>2.326841535861557</ns0:v>
+      </ns0:c>
+      <ns0:c r="I70">
+        <ns0:v>76.02999877929688</ns0:v>
+      </ns0:c>
+      <ns0:c r="J70">
+        <ns0:v>-0.5129546177957245</ns0:v>
+      </ns0:c>
+      <ns0:c r="K70">
+        <ns0:v>0.9766659873649888</ns0:v>
+      </ns0:c>
+      <ns0:c r="L70">
+        <ns0:v>71.914270872721</ns0:v>
+      </ns0:c>
+      <ns0:c r="M70">
+        <ns0:v>69.84600028991699</ns0:v>
+      </ns0:c>
+      <ns0:c r="N70">
+        <ns0:v>62.25060028076172</ns0:v>
+      </ns0:c>
+      <ns0:c r="O70">
+        <ns0:v>54.86120004653931</ns0:v>
+      </ns0:c>
+      <ns0:c r="P70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>재료 수집 실패</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R70" t="inlineStr">
+        <ns0:is>
+          <ns0:t/>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T70" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/VEON/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="71">
+      <ns0:c r="A71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-10-02</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>VRA</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Vera Bradley Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Consumer Cyclical</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Footwear &amp; Accessories</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>미국에서 여성용 핸드백, 여행 가방·용품, 패션·홈 액세서리와 선물용품을 디자인·제조한다.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G71">
+        <ns0:v>5.110000133514404</ns0:v>
+      </ns0:c>
+      <ns0:c r="H71">
+        <ns0:v>2.6104440550806185</ns0:v>
+      </ns0:c>
+      <ns0:c r="I71">
+        <ns0:v>5.110000133514404</ns0:v>
+      </ns0:c>
+      <ns0:c r="J71">
+        <ns0:v>0.0</ns0:v>
+      </ns0:c>
+      <ns0:c r="K71">
+        <ns0:v>0.4454140262875404</ns0:v>
+      </ns0:c>
+      <ns0:c r="L71">
+        <ns0:v>77.16253272002446</ns0:v>
+      </ns0:c>
+      <ns0:c r="M71">
+        <ns0:v>3.9680000066757204</ns0:v>
+      </ns0:c>
+      <ns0:c r="N71">
+        <ns0:v>3.5978000164031982</ns0:v>
+      </ns0:c>
+      <ns0:c r="O71">
+        <ns0:v>3.3451500058174135</ns0:v>
+      </ns0:c>
+      <ns0:c r="P71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>재료 수집 실패</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R71" t="inlineStr">
+        <ns0:is>
+          <ns0:t/>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T71" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/VRA/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="72">
+      <ns0:c r="A72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-10-02</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>WEYS</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Weyco Group Inc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Consumer Cyclical</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Footwear &amp; Accessories</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>미국·캐나다·호주·아시아·남아프리카에서 남성·여성·아동용 신발을 디자인·마케팅·유통.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G72">
+        <ns0:v>50.88999938964844</ns0:v>
+      </ns0:c>
+      <ns0:c r="H72">
+        <ns0:v>1.3543125225550234</ns0:v>
+      </ns0:c>
+      <ns0:c r="I72">
+        <ns0:v>50.47999954223633</ns0:v>
+      </ns0:c>
+      <ns0:c r="J72">
+        <ns0:v>0.8122025577061764</ns0:v>
+      </ns0:c>
+      <ns0:c r="K72">
+        <ns0:v>0.8833657733193592</ns0:v>
+      </ns0:c>
+      <ns0:c r="L72">
+        <ns0:v>74.85120169757123</ns0:v>
+      </ns0:c>
+      <ns0:c r="M72">
+        <ns0:v>46.14900016784668</ns0:v>
+      </ns0:c>
+      <ns0:c r="N72">
+        <ns0:v>44.68260017395019</ns0:v>
+      </ns0:c>
+      <ns0:c r="O72">
+        <ns0:v>36.55820008277893</ns0:v>
+      </ns0:c>
+      <ns0:c r="P72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>종가 돌파</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>재료 수집 실패</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R72" t="inlineStr">
+        <ns0:is>
+          <ns0:t/>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T72" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/WEYS/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="73">
+      <ns0:c r="A73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-10-02</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>WTBA</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>West Bancorporation</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Financial</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Banks - Regional</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>미국 개인과 중소기업에 예금 등 지역 금융·신탁 서비스를 제공하는 웨스트뱅크의 은행지주회사.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G73">
+        <ns0:v>30.079999923706055</ns0:v>
+      </ns0:c>
+      <ns0:c r="H73">
+        <ns0:v>4.155127416241933</ns0:v>
+      </ns0:c>
+      <ns0:c r="I73">
+        <ns0:v>30.329999923706055</ns0:v>
+      </ns0:c>
+      <ns0:c r="J73">
+        <ns0:v>-0.8242664049748272</ns0:v>
+      </ns0:c>
+      <ns0:c r="K73">
+        <ns0:v>2.460309730203565</ns0:v>
+      </ns0:c>
+      <ns0:c r="L73">
+        <ns0:v>62.98668498653244</ns0:v>
+      </ns0:c>
+      <ns0:c r="M73">
+        <ns0:v>29.167000007629394</ns0:v>
+      </ns0:c>
+      <ns0:c r="N73">
+        <ns0:v>28.782399978637695</ns0:v>
+      </ns0:c>
+      <ns0:c r="O73">
+        <ns0:v>25.433200006484984</ns0:v>
+      </ns0:c>
+      <ns0:c r="P73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장중 경신 후 밀림</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>재료 수집 실패</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R73" t="inlineStr">
+        <ns0:is>
+          <ns0:t/>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T73" t="inlineStr">
+        <ns0:is>
+          <ns0:t>https://finance.yahoo.com/quote/WTBA/profile/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="74">
+      <ns0:c r="A74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>2026-10-02</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B74" t="inlineStr">
+        <ns0:is>
           <ns0:t>XRPN</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="C68" t="inlineStr">
+      <ns0:c r="C74" t="inlineStr">
         <ns0:is>
           <ns0:t>Armada Acquisition Corp II</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="D68" t="inlineStr">
+      <ns0:c r="D74" t="inlineStr">
         <ns0:is>
           <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="E68" t="inlineStr">
+      <ns0:c r="E74" t="inlineStr">
         <ns0:is>
           <ns0:t>Shell Companies</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="F68" t="inlineStr">
+      <ns0:c r="F74" t="inlineStr">
         <ns0:is>
           <ns0:t>기술 서비스 분야 기업과의 합병·주식 교환·자산 인수 등 사업결합을 추진한다.</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="G68">
+      <ns0:c r="G74">
         <ns0:v>39.41999816894531</ns0:v>
       </ns0:c>
-      <ns0:c r="H68">
+      <ns0:c r="H74">
         <ns0:v>68.24582866197093</ns0:v>
       </ns0:c>
-      <ns0:c r="I68">
+      <ns0:c r="I74">
         <ns0:v>23.989999771118164</ns0:v>
       </ns0:c>
-      <ns0:c r="J68">
+      <ns0:c r="J74">
         <ns0:v>64.31845996265287</ns0:v>
       </ns0:c>
-      <ns0:c r="K68">
-        <ns0:v>14.057668037571439</ns0:v>
-      </ns0:c>
-      <ns0:c r="L68">
+      <ns0:c r="K74">
+        <ns0:v>14.120573490923796</ns0:v>
+      </ns0:c>
+      <ns0:c r="L74">
         <ns0:v>99.89432913168544</ns0:v>
       </ns0:c>
-      <ns0:c r="M68">
+      <ns0:c r="M74">
         <ns0:v>13.050749826431275</ns0:v>
       </ns0:c>
-      <ns0:c r="N68">
+      <ns0:c r="N74">
         <ns0:v>11.51601993560791</ns0:v>
       </ns0:c>
-      <ns0:c r="O68">
+      <ns0:c r="O74">
         <ns0:v>10.62946997642517</ns0:v>
       </ns0:c>
-      <ns0:c r="P68" t="inlineStr">
+      <ns0:c r="P74" t="inlineStr">
         <ns0:is>
           <ns0:t>종가 돌파</ns0:t>
         </ns0:is>
       </ns0:c>
-      <ns0:c r="Q68" t="inlineStr">
-        <ns0:is>
-          <ns0:t>재료 수집 실패</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="R68" t="inlineStr">
-        <ns0:is>
-          <ns0:t/>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="T68" t="inlineStr">
+      <ns0:c r="Q74" t="inlineStr">
+        <ns0:is>
+          <ns0:t>재료 수집 실패</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="R74" t="inlineStr">
+        <ns0:is>
+          <ns0:t/>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="T74" t="inlineStr">
         <ns0:is>
           <ns0:t>https://finance.yahoo.com/quote/XRPN/profile/</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
   </ns0:sheetData>
-  <ns0:autoFilter ref="A1:T68"/>
+  <ns0:autoFilter ref="A1:T74"/>
   <ns0:hyperlinks>
     <ns0:hyperlink ref="S2" ns1:id="rId1"/>
     <ns0:hyperlink ref="T2" ns1:id="rId2"/>
@@ -5473,6 +5944,12 @@
     <ns0:hyperlink ref="T66" ns1:id="rId67"/>
     <ns0:hyperlink ref="T67" ns1:id="rId68"/>
     <ns0:hyperlink ref="T68" ns1:id="rId69"/>
+    <ns0:hyperlink ref="T69" ns1:id="rId70"/>
+    <ns0:hyperlink ref="T70" ns1:id="rId71"/>
+    <ns0:hyperlink ref="T71" ns1:id="rId72"/>
+    <ns0:hyperlink ref="T72" ns1:id="rId73"/>
+    <ns0:hyperlink ref="T73" ns1:id="rId74"/>
+    <ns0:hyperlink ref="T74" ns1:id="rId75"/>
   </ns0:hyperlinks>
 </ns0:worksheet>
 </file>
@@ -5509,7 +5986,7 @@
         </ns0:is>
       </ns0:c>
       <ns0:c r="C2">
-        <ns0:v>25</ns0:v>
+        <ns0:v>26</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="3">
@@ -5524,7 +6001,7 @@
         </ns0:is>
       </ns0:c>
       <ns0:c r="C3">
-        <ns0:v>9</ns0:v>
+        <ns0:v>12</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="4">
@@ -5539,7 +6016,7 @@
         </ns0:is>
       </ns0:c>
       <ns0:c r="C4">
-        <ns0:v>8</ns0:v>
+        <ns0:v>9</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="5">
@@ -5550,11 +6027,11 @@
       </ns0:c>
       <ns0:c r="B5" t="inlineStr">
         <ns0:is>
-          <ns0:t>Energy</ns0:t>
+          <ns0:t>Financial</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C5">
-        <ns0:v>7</ns0:v>
+        <ns0:v>8</ns0:v>
       </ns0:c>
     </ns0:row>
     <ns0:row r="6">
@@ -5565,7 +6042,7 @@
       </ns0:c>
       <ns0:c r="B6" t="inlineStr">
         <ns0:is>
-          <ns0:t>Financial</ns0:t>
+          <ns0:t>Energy</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="C6">
@@ -5704,7 +6181,7 @@
         </ns0:is>
       </ns0:c>
       <ns0:c r="C2">
-        <ns0:v>67</ns0:v>
+        <ns0:v>73</ns0:v>
       </ns0:c>
       <ns0:c r="D2" t="inlineStr">
         <ns0:is>
